--- a/research/traditional_assets/database/data/slovenia/slovenia_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09467086218488646</v>
+        <v>0.09452743754673518</v>
       </c>
       <c r="C2">
-        <v>253.7825351654178</v>
+        <v>251.9567314477948</v>
       </c>
       <c r="D2">
-        <v>242.9825351654177</v>
+        <v>243.6977314477948</v>
       </c>
       <c r="E2">
-        <v>-24</v>
+        <v>-21.459</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.541</v>
       </c>
       <c r="G2">
         <v>10.8</v>
@@ -1451,28 +1451,28 @@
         <v>19.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1278123</v>
       </c>
       <c r="N2">
-        <v>19.2</v>
+        <v>19.0721877</v>
       </c>
       <c r="O2">
-        <v>3.648</v>
+        <v>3.623715663</v>
       </c>
       <c r="P2">
-        <v>15.552</v>
+        <v>15.448472037</v>
       </c>
       <c r="Q2">
-        <v>21.652</v>
+        <v>21.548472037</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09467086218488646</v>
+        <v>0.0950707146936719</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8307750331087227</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>150.2202839632805</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09452743754673518</v>
+        <v>0.09438401290858389</v>
       </c>
       <c r="C3">
-        <v>251.9567314477948</v>
+        <v>250.1351503853979</v>
       </c>
       <c r="D3">
-        <v>243.6977314477948</v>
+        <v>244.4171503853979</v>
       </c>
       <c r="E3">
-        <v>-21.459</v>
+        <v>-18.918</v>
       </c>
       <c r="F3">
-        <v>2.541</v>
+        <v>5.082</v>
       </c>
       <c r="G3">
         <v>10.8</v>
@@ -1533,28 +1533,28 @@
         <v>19.2</v>
       </c>
       <c r="M3">
-        <v>0.1278123</v>
+        <v>0.2556246</v>
       </c>
       <c r="N3">
-        <v>19.0721877</v>
+        <v>18.9443754</v>
       </c>
       <c r="O3">
-        <v>3.623715663</v>
+        <v>3.599431326</v>
       </c>
       <c r="P3">
-        <v>15.448472037</v>
+        <v>15.344944074</v>
       </c>
       <c r="Q3">
-        <v>21.548472037</v>
+        <v>21.444944074</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0950707146936719</v>
+        <v>0.09547872745773867</v>
       </c>
       <c r="T3">
-        <v>0.8307750331087227</v>
+        <v>0.8376547144708419</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>150.2202839632805</v>
+        <v>75.11014198164027</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09438401290858389</v>
+        <v>0.09424058827043262</v>
       </c>
       <c r="C4">
-        <v>250.1351503853979</v>
+        <v>248.317829485996</v>
       </c>
       <c r="D4">
-        <v>244.4171503853979</v>
+        <v>245.140829485996</v>
       </c>
       <c r="E4">
-        <v>-18.918</v>
+        <v>-16.377</v>
       </c>
       <c r="F4">
-        <v>5.082</v>
+        <v>7.622999999999999</v>
       </c>
       <c r="G4">
         <v>10.8</v>
@@ -1615,28 +1615,28 @@
         <v>19.2</v>
       </c>
       <c r="M4">
-        <v>0.2556246</v>
+        <v>0.3834369</v>
       </c>
       <c r="N4">
-        <v>18.9443754</v>
+        <v>18.8165631</v>
       </c>
       <c r="O4">
-        <v>3.599431326</v>
+        <v>3.575146989</v>
       </c>
       <c r="P4">
-        <v>15.344944074</v>
+        <v>15.241416111</v>
       </c>
       <c r="Q4">
-        <v>21.444944074</v>
+        <v>21.341416111</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09547872745773867</v>
+        <v>0.09589515285611611</v>
       </c>
       <c r="T4">
-        <v>0.8376547144708419</v>
+        <v>0.8446762449332111</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>75.11014198164027</v>
+        <v>50.07342798776018</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09424058827043262</v>
+        <v>0.09409716363228132</v>
       </c>
       <c r="C5">
-        <v>248.317829485996</v>
+        <v>246.5048067028949</v>
       </c>
       <c r="D5">
-        <v>245.140829485996</v>
+        <v>245.8688067028949</v>
       </c>
       <c r="E5">
-        <v>-16.377</v>
+        <v>-13.836</v>
       </c>
       <c r="F5">
-        <v>7.622999999999999</v>
+        <v>10.164</v>
       </c>
       <c r="G5">
         <v>10.8</v>
@@ -1697,28 +1697,28 @@
         <v>19.2</v>
       </c>
       <c r="M5">
-        <v>0.3834369</v>
+        <v>0.5112492</v>
       </c>
       <c r="N5">
-        <v>18.8165631</v>
+        <v>18.6887508</v>
       </c>
       <c r="O5">
-        <v>3.575146989</v>
+        <v>3.550862652</v>
       </c>
       <c r="P5">
-        <v>15.241416111</v>
+        <v>15.137888148</v>
       </c>
       <c r="Q5">
-        <v>21.341416111</v>
+        <v>21.237888148</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09589515285611611</v>
+        <v>0.09632025378362638</v>
       </c>
       <c r="T5">
-        <v>0.8446762449332111</v>
+        <v>0.8518440572802128</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>50.07342798776018</v>
+        <v>37.55507099082013</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09409716363228132</v>
+        <v>0.09395373899413004</v>
       </c>
       <c r="C6">
-        <v>246.5048067028949</v>
+        <v>244.6961204415715</v>
       </c>
       <c r="D6">
-        <v>245.8688067028949</v>
+        <v>246.6011204415715</v>
       </c>
       <c r="E6">
-        <v>-13.836</v>
+        <v>-11.295</v>
       </c>
       <c r="F6">
-        <v>10.164</v>
+        <v>12.705</v>
       </c>
       <c r="G6">
         <v>10.8</v>
@@ -1779,28 +1779,28 @@
         <v>19.2</v>
       </c>
       <c r="M6">
-        <v>0.5112492</v>
+        <v>0.6390614999999999</v>
       </c>
       <c r="N6">
-        <v>18.6887508</v>
+        <v>18.5609385</v>
       </c>
       <c r="O6">
-        <v>3.550862652</v>
+        <v>3.526578315</v>
       </c>
       <c r="P6">
-        <v>15.137888148</v>
+        <v>15.034360185</v>
       </c>
       <c r="Q6">
-        <v>21.237888148</v>
+        <v>21.134360185</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09632025378362638</v>
+        <v>0.09675430420434741</v>
       </c>
       <c r="T6">
-        <v>0.8518440572802128</v>
+        <v>0.8591627709397832</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.55507099082013</v>
+        <v>30.04405679265611</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09395373899413004</v>
+        <v>0.09381031435597875</v>
       </c>
       <c r="C7">
-        <v>244.6961204415715</v>
+        <v>242.8918095664289</v>
       </c>
       <c r="D7">
-        <v>246.6011204415715</v>
+        <v>247.3378095664289</v>
       </c>
       <c r="E7">
-        <v>-11.295</v>
+        <v>-8.754</v>
       </c>
       <c r="F7">
-        <v>12.705</v>
+        <v>15.246</v>
       </c>
       <c r="G7">
         <v>10.8</v>
@@ -1861,28 +1861,28 @@
         <v>19.2</v>
       </c>
       <c r="M7">
-        <v>0.6390614999999999</v>
+        <v>0.7668737999999999</v>
       </c>
       <c r="N7">
-        <v>18.5609385</v>
+        <v>18.4331262</v>
       </c>
       <c r="O7">
-        <v>3.526578315</v>
+        <v>3.502293978</v>
       </c>
       <c r="P7">
-        <v>15.034360185</v>
+        <v>14.930832222</v>
       </c>
       <c r="Q7">
-        <v>21.134360185</v>
+        <v>21.030832222</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09675430420434741</v>
+        <v>0.09719758974040293</v>
       </c>
       <c r="T7">
-        <v>0.8591627709397832</v>
+        <v>0.8666372019112593</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.04405679265611</v>
+        <v>25.03671399388009</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09381031435597875</v>
+        <v>0.09366688971782748</v>
       </c>
       <c r="C8">
-        <v>242.8918095664289</v>
+        <v>241.0919134076709</v>
       </c>
       <c r="D8">
-        <v>247.3378095664289</v>
+        <v>248.0789134076709</v>
       </c>
       <c r="E8">
-        <v>-8.754000000000001</v>
+        <v>-6.213000000000001</v>
       </c>
       <c r="F8">
-        <v>15.246</v>
+        <v>17.787</v>
       </c>
       <c r="G8">
         <v>10.8</v>
@@ -1943,28 +1943,28 @@
         <v>19.2</v>
       </c>
       <c r="M8">
-        <v>0.7668737999999999</v>
+        <v>0.8946860999999999</v>
       </c>
       <c r="N8">
-        <v>18.4331262</v>
+        <v>18.3053139</v>
       </c>
       <c r="O8">
-        <v>3.502293978</v>
+        <v>3.478009641</v>
       </c>
       <c r="P8">
-        <v>14.930832222</v>
+        <v>14.827304259</v>
       </c>
       <c r="Q8">
-        <v>21.030832222</v>
+        <v>20.927304259</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09719758974040293</v>
+        <v>0.09765040829873922</v>
       </c>
       <c r="T8">
-        <v>0.8666372019112593</v>
+        <v>0.874272373333735</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.03671399388009</v>
+        <v>21.46004056618293</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09366688971782747</v>
+        <v>0.0935234650796762</v>
       </c>
       <c r="C9">
-        <v>241.0919134076711</v>
+        <v>239.2964717683025</v>
       </c>
       <c r="D9">
-        <v>248.0789134076711</v>
+        <v>248.8244717683025</v>
       </c>
       <c r="E9">
-        <v>-6.212999999999997</v>
+        <v>-3.672000000000001</v>
       </c>
       <c r="F9">
-        <v>17.787</v>
+        <v>20.328</v>
       </c>
       <c r="G9">
         <v>10.8</v>
@@ -2025,28 +2025,28 @@
         <v>19.2</v>
       </c>
       <c r="M9">
-        <v>0.8946861</v>
+        <v>1.0224984</v>
       </c>
       <c r="N9">
-        <v>18.3053139</v>
+        <v>18.1775016</v>
       </c>
       <c r="O9">
-        <v>3.478009641</v>
+        <v>3.453725304</v>
       </c>
       <c r="P9">
-        <v>14.827304259</v>
+        <v>14.723776296</v>
       </c>
       <c r="Q9">
-        <v>20.927304259</v>
+        <v>20.823776296</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09765040829873922</v>
+        <v>0.09811307073877847</v>
       </c>
       <c r="T9">
-        <v>0.874272373333735</v>
+        <v>0.8820735267436557</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.46004056618293</v>
+        <v>18.77753549541007</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0935234650796762</v>
+        <v>0.0933800404415249</v>
       </c>
       <c r="C10">
-        <v>239.2964717683025</v>
+        <v>237.5055249312547</v>
       </c>
       <c r="D10">
-        <v>248.8244717683025</v>
+        <v>249.5745249312546</v>
       </c>
       <c r="E10">
-        <v>-3.672000000000001</v>
+        <v>-1.131</v>
       </c>
       <c r="F10">
-        <v>20.328</v>
+        <v>22.869</v>
       </c>
       <c r="G10">
         <v>10.8</v>
@@ -2107,28 +2107,28 @@
         <v>19.2</v>
       </c>
       <c r="M10">
-        <v>1.0224984</v>
+        <v>1.1503107</v>
       </c>
       <c r="N10">
-        <v>18.1775016</v>
+        <v>18.0496893</v>
       </c>
       <c r="O10">
-        <v>3.453725304</v>
+        <v>3.429440967</v>
       </c>
       <c r="P10">
-        <v>14.723776296</v>
+        <v>14.620248333</v>
       </c>
       <c r="Q10">
-        <v>20.823776296</v>
+        <v>20.720248333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09811307073877847</v>
+        <v>0.09858590158409329</v>
       </c>
       <c r="T10">
-        <v>0.8820735267436557</v>
+        <v>0.8900461340746734</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.77753549541007</v>
+        <v>16.69114266258673</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0933800404415249</v>
+        <v>0.09323661580337363</v>
       </c>
       <c r="C11">
-        <v>237.5055249312547</v>
+        <v>235.7191136666403</v>
       </c>
       <c r="D11">
-        <v>249.5745249312546</v>
+        <v>250.3291136666402</v>
       </c>
       <c r="E11">
-        <v>-1.131</v>
+        <v>1.409999999999997</v>
       </c>
       <c r="F11">
-        <v>22.869</v>
+        <v>25.41</v>
       </c>
       <c r="G11">
         <v>10.8</v>
@@ -2189,28 +2189,28 @@
         <v>19.2</v>
       </c>
       <c r="M11">
-        <v>1.1503107</v>
+        <v>1.278123</v>
       </c>
       <c r="N11">
-        <v>18.0496893</v>
+        <v>17.921877</v>
       </c>
       <c r="O11">
-        <v>3.429440967</v>
+        <v>3.40515663</v>
       </c>
       <c r="P11">
-        <v>14.620248333</v>
+        <v>14.51672037</v>
       </c>
       <c r="Q11">
-        <v>20.720248333</v>
+        <v>20.61672037</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09858590158409329</v>
+        <v>0.09906923978152625</v>
       </c>
       <c r="T11">
-        <v>0.8900461340746734</v>
+        <v>0.8981959104574918</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.69114266258673</v>
+        <v>15.02202839632806</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09323661580337363</v>
+        <v>0.09309319116522234</v>
       </c>
       <c r="C12">
-        <v>235.7191136666403</v>
+        <v>233.9372792391418</v>
       </c>
       <c r="D12">
-        <v>250.3291136666402</v>
+        <v>251.0882792391417</v>
       </c>
       <c r="E12">
-        <v>1.41</v>
+        <v>3.951000000000001</v>
       </c>
       <c r="F12">
-        <v>25.41</v>
+        <v>27.951</v>
       </c>
       <c r="G12">
         <v>10.8</v>
@@ -2271,28 +2271,28 @@
         <v>19.2</v>
       </c>
       <c r="M12">
-        <v>1.278123</v>
+        <v>1.4059353</v>
       </c>
       <c r="N12">
-        <v>17.921877</v>
+        <v>17.7940647</v>
       </c>
       <c r="O12">
-        <v>3.40515663</v>
+        <v>3.380872293</v>
       </c>
       <c r="P12">
-        <v>14.51672037</v>
+        <v>14.413192407</v>
       </c>
       <c r="Q12">
-        <v>20.61672037</v>
+        <v>20.513192407</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09906923978152625</v>
+        <v>0.09956343951148577</v>
       </c>
       <c r="T12">
-        <v>0.8981959104574918</v>
+        <v>0.9065288278826205</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.02202839632805</v>
+        <v>13.65638945120732</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09309319116522234</v>
+        <v>0.09309556652707106</v>
       </c>
       <c r="C13">
-        <v>233.9372792391418</v>
+        <v>231.3836686381286</v>
       </c>
       <c r="D13">
-        <v>251.0882792391417</v>
+        <v>251.0756686381286</v>
       </c>
       <c r="E13">
-        <v>3.951000000000001</v>
+        <v>6.491999999999997</v>
       </c>
       <c r="F13">
-        <v>27.951</v>
+        <v>30.492</v>
       </c>
       <c r="G13">
         <v>10.8</v>
@@ -2353,45 +2353,45 @@
         <v>19.2</v>
       </c>
       <c r="M13">
-        <v>1.4059353</v>
+        <v>1.5794856</v>
       </c>
       <c r="N13">
-        <v>17.7940647</v>
+        <v>17.6205144</v>
       </c>
       <c r="O13">
-        <v>3.380872293</v>
+        <v>3.347897736</v>
       </c>
       <c r="P13">
-        <v>14.413192407</v>
+        <v>14.272616664</v>
       </c>
       <c r="Q13">
-        <v>20.513192407</v>
+        <v>20.372616664</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09956343951148577</v>
+        <v>0.1000688710534898</v>
       </c>
       <c r="T13">
-        <v>0.9065288278826205</v>
+        <v>0.9150511297946839</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.65638945120732</v>
+        <v>12.15585631170047</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09309556652707106</v>
+        <v>0.09296429188891978</v>
       </c>
       <c r="C14">
-        <v>231.3836686381286</v>
+        <v>229.5414996017459</v>
       </c>
       <c r="D14">
-        <v>251.0756686381286</v>
+        <v>251.7744996017459</v>
       </c>
       <c r="E14">
-        <v>6.491999999999997</v>
+        <v>9.033000000000001</v>
       </c>
       <c r="F14">
-        <v>30.492</v>
+        <v>33.033</v>
       </c>
       <c r="G14">
         <v>10.8</v>
@@ -2435,28 +2435,28 @@
         <v>19.2</v>
       </c>
       <c r="M14">
-        <v>1.5794856</v>
+        <v>1.7111094</v>
       </c>
       <c r="N14">
-        <v>17.6205144</v>
+        <v>17.4888906</v>
       </c>
       <c r="O14">
-        <v>3.347897736</v>
+        <v>3.322889213999999</v>
       </c>
       <c r="P14">
-        <v>14.272616664</v>
+        <v>14.166001386</v>
       </c>
       <c r="Q14">
-        <v>20.372616664</v>
+        <v>20.266001386</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1000688710534898</v>
+        <v>0.100585921711402</v>
       </c>
       <c r="T14">
-        <v>0.9150511297946839</v>
+        <v>0.9237693466932319</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.15585631170047</v>
+        <v>11.22079044156966</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09296429188891978</v>
+        <v>0.09283301725076848</v>
       </c>
       <c r="C15">
-        <v>229.5414996017459</v>
+        <v>227.7032316028574</v>
       </c>
       <c r="D15">
-        <v>251.7744996017459</v>
+        <v>252.4772316028574</v>
       </c>
       <c r="E15">
-        <v>9.033000000000001</v>
+        <v>11.57400000000001</v>
       </c>
       <c r="F15">
-        <v>33.033</v>
+        <v>35.57400000000001</v>
       </c>
       <c r="G15">
         <v>10.8</v>
@@ -2517,28 +2517,28 @@
         <v>19.2</v>
       </c>
       <c r="M15">
-        <v>1.7111094</v>
+        <v>1.8427332</v>
       </c>
       <c r="N15">
-        <v>17.4888906</v>
+        <v>17.3572668</v>
       </c>
       <c r="O15">
-        <v>3.322889213999999</v>
+        <v>3.297880692</v>
       </c>
       <c r="P15">
-        <v>14.166001386</v>
+        <v>14.059386108</v>
       </c>
       <c r="Q15">
-        <v>20.266001386</v>
+        <v>20.159386108</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.100585921711402</v>
+        <v>0.1011149968032192</v>
       </c>
       <c r="T15">
-        <v>0.9237693466932319</v>
+        <v>0.9326903128219783</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.22079044156966</v>
+        <v>10.41930541002897</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09283301725076848</v>
+        <v>0.0929082926126172</v>
       </c>
       <c r="C16">
-        <v>227.7032316028574</v>
+        <v>224.7587927619774</v>
       </c>
       <c r="D16">
-        <v>252.4772316028574</v>
+        <v>252.0737927619774</v>
       </c>
       <c r="E16">
-        <v>11.57400000000001</v>
+        <v>14.115</v>
       </c>
       <c r="F16">
-        <v>35.57400000000001</v>
+        <v>38.115</v>
       </c>
       <c r="G16">
         <v>10.8</v>
@@ -2599,45 +2599,45 @@
         <v>19.2</v>
       </c>
       <c r="M16">
-        <v>1.8427332</v>
+        <v>2.0391525</v>
       </c>
       <c r="N16">
-        <v>17.3572668</v>
+        <v>17.1608475</v>
       </c>
       <c r="O16">
-        <v>3.297880692</v>
+        <v>3.260561025</v>
       </c>
       <c r="P16">
-        <v>14.059386108</v>
+        <v>13.900286475</v>
       </c>
       <c r="Q16">
-        <v>20.159386108</v>
+        <v>20.000286475</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1011149968032192</v>
+        <v>0.1016565207207261</v>
       </c>
       <c r="T16">
-        <v>0.9326903128219783</v>
+        <v>0.9418211840361072</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.41930541002897</v>
+        <v>9.415676365548922</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0929082926126172</v>
+        <v>0.09279078797446592</v>
       </c>
       <c r="C17">
-        <v>224.7587927619774</v>
+        <v>222.8481256651415</v>
       </c>
       <c r="D17">
-        <v>252.0737927619774</v>
+        <v>252.7041256651416</v>
       </c>
       <c r="E17">
-        <v>14.11499999999999</v>
+        <v>16.656</v>
       </c>
       <c r="F17">
-        <v>38.11499999999999</v>
+        <v>40.656</v>
       </c>
       <c r="G17">
         <v>10.8</v>
@@ -2681,28 +2681,28 @@
         <v>19.2</v>
       </c>
       <c r="M17">
-        <v>2.0391525</v>
+        <v>2.175096</v>
       </c>
       <c r="N17">
-        <v>17.1608475</v>
+        <v>17.024904</v>
       </c>
       <c r="O17">
-        <v>3.260561025</v>
+        <v>3.23473176</v>
       </c>
       <c r="P17">
-        <v>13.900286475</v>
+        <v>13.79017224</v>
       </c>
       <c r="Q17">
-        <v>20.000286475</v>
+        <v>19.89017224</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1016565207207261</v>
+        <v>0.1022109380648404</v>
       </c>
       <c r="T17">
-        <v>0.9418211840361072</v>
+        <v>0.9511694569458105</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.415676365548924</v>
+        <v>8.827196592702116</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09279078797446592</v>
+        <v>0.09267328333631462</v>
       </c>
       <c r="C18">
-        <v>222.8481256651415</v>
+        <v>220.9406188777371</v>
       </c>
       <c r="D18">
-        <v>252.7041256651416</v>
+        <v>253.3376188777371</v>
       </c>
       <c r="E18">
-        <v>16.656</v>
+        <v>19.197</v>
       </c>
       <c r="F18">
-        <v>40.656</v>
+        <v>43.197</v>
       </c>
       <c r="G18">
         <v>10.8</v>
@@ -2763,28 +2763,28 @@
         <v>19.2</v>
       </c>
       <c r="M18">
-        <v>2.175096</v>
+        <v>2.3110395</v>
       </c>
       <c r="N18">
-        <v>17.024904</v>
+        <v>16.8889605</v>
       </c>
       <c r="O18">
-        <v>3.23473176</v>
+        <v>3.208902495</v>
       </c>
       <c r="P18">
-        <v>13.79017224</v>
+        <v>13.680058005</v>
       </c>
       <c r="Q18">
-        <v>19.89017224</v>
+        <v>19.780058005</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1022109380648404</v>
+        <v>0.1027787148630297</v>
       </c>
       <c r="T18">
-        <v>0.9511694569458105</v>
+        <v>0.9607429894436994</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.827196592702116</v>
+        <v>8.307949734307872</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09267328333631462</v>
+        <v>0.09255577869816332</v>
       </c>
       <c r="C19">
-        <v>220.9406188777371</v>
+        <v>219.0362962268304</v>
       </c>
       <c r="D19">
-        <v>253.3376188777371</v>
+        <v>253.9742962268304</v>
       </c>
       <c r="E19">
-        <v>19.197</v>
+        <v>21.73800000000001</v>
       </c>
       <c r="F19">
-        <v>43.197</v>
+        <v>45.73800000000001</v>
       </c>
       <c r="G19">
         <v>10.8</v>
@@ -2845,28 +2845,28 @@
         <v>19.2</v>
       </c>
       <c r="M19">
-        <v>2.3110395</v>
+        <v>2.446983</v>
       </c>
       <c r="N19">
-        <v>16.8889605</v>
+        <v>16.753017</v>
       </c>
       <c r="O19">
-        <v>3.208902495</v>
+        <v>3.18307323</v>
       </c>
       <c r="P19">
-        <v>13.680058005</v>
+        <v>13.56994377</v>
       </c>
       <c r="Q19">
-        <v>19.780058005</v>
+        <v>19.66994377</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1027787148630297</v>
+        <v>0.1033603398758089</v>
       </c>
       <c r="T19">
-        <v>0.9607429894436994</v>
+        <v>0.9705500227342196</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.307949734307872</v>
+        <v>7.846396971290768</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09255577869816334</v>
+        <v>0.09256139406001207</v>
       </c>
       <c r="C20">
-        <v>219.0362962268304</v>
+        <v>216.4647976156948</v>
       </c>
       <c r="D20">
-        <v>253.9742962268304</v>
+        <v>253.9437976156948</v>
       </c>
       <c r="E20">
-        <v>21.738</v>
+        <v>24.279</v>
       </c>
       <c r="F20">
-        <v>45.738</v>
+        <v>48.279</v>
       </c>
       <c r="G20">
         <v>10.8</v>
@@ -2927,45 +2927,45 @@
         <v>19.2</v>
       </c>
       <c r="M20">
-        <v>2.446983</v>
+        <v>2.6215497</v>
       </c>
       <c r="N20">
-        <v>16.753017</v>
+        <v>16.5784503</v>
       </c>
       <c r="O20">
-        <v>3.18307323</v>
+        <v>3.149905557</v>
       </c>
       <c r="P20">
-        <v>13.56994377</v>
+        <v>13.428544743</v>
       </c>
       <c r="Q20">
-        <v>19.66994377</v>
+        <v>19.528544743</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1033603398758089</v>
+        <v>0.1039563260000149</v>
       </c>
       <c r="T20">
-        <v>0.9705500227342196</v>
+        <v>0.9805992049948763</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.846396971290769</v>
+        <v>7.323912264566261</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09256139406001207</v>
+        <v>0.09245036942186079</v>
       </c>
       <c r="C21">
-        <v>216.4647976156948</v>
+        <v>214.5281662110662</v>
       </c>
       <c r="D21">
-        <v>253.9437976156948</v>
+        <v>254.5481662110662</v>
       </c>
       <c r="E21">
-        <v>24.279</v>
+        <v>26.82</v>
       </c>
       <c r="F21">
-        <v>48.279</v>
+        <v>50.82</v>
       </c>
       <c r="G21">
         <v>10.8</v>
@@ -3009,28 +3009,28 @@
         <v>19.2</v>
       </c>
       <c r="M21">
-        <v>2.6215497</v>
+        <v>2.759526</v>
       </c>
       <c r="N21">
-        <v>16.5784503</v>
+        <v>16.440474</v>
       </c>
       <c r="O21">
-        <v>3.149905557</v>
+        <v>3.123690059999999</v>
       </c>
       <c r="P21">
-        <v>13.428544743</v>
+        <v>13.31678394</v>
       </c>
       <c r="Q21">
-        <v>19.528544743</v>
+        <v>19.41678394</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1039563260000149</v>
+        <v>0.104567211777326</v>
       </c>
       <c r="T21">
-        <v>0.9805992049948763</v>
+        <v>0.9908996168120495</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.323912264566261</v>
+        <v>6.957716651337946</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09245036942186079</v>
+        <v>0.0923393447837095</v>
       </c>
       <c r="C22">
-        <v>214.5281662110662</v>
+        <v>212.5944183796774</v>
       </c>
       <c r="D22">
-        <v>254.5481662110662</v>
+        <v>255.1554183796775</v>
       </c>
       <c r="E22">
-        <v>26.82</v>
+        <v>29.361</v>
       </c>
       <c r="F22">
-        <v>50.82</v>
+        <v>53.361</v>
       </c>
       <c r="G22">
         <v>10.8</v>
@@ -3091,28 +3091,28 @@
         <v>19.2</v>
       </c>
       <c r="M22">
-        <v>2.759526</v>
+        <v>2.8975023</v>
       </c>
       <c r="N22">
-        <v>16.440474</v>
+        <v>16.3024977</v>
       </c>
       <c r="O22">
-        <v>3.123690059999999</v>
+        <v>3.097474563</v>
       </c>
       <c r="P22">
-        <v>13.31678394</v>
+        <v>13.205023137</v>
       </c>
       <c r="Q22">
-        <v>19.41678394</v>
+        <v>19.305023137</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.104567211777326</v>
+        <v>0.1051935630173538</v>
       </c>
       <c r="T22">
-        <v>0.9908996168120495</v>
+        <v>1.001460798548645</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.957716651337946</v>
+        <v>6.626396810798044</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0923393447837095</v>
+        <v>0.09222832014555823</v>
       </c>
       <c r="C23">
-        <v>212.5944183796774</v>
+        <v>210.6635748081058</v>
       </c>
       <c r="D23">
-        <v>255.1554183796775</v>
+        <v>255.7655748081058</v>
       </c>
       <c r="E23">
-        <v>29.361</v>
+        <v>31.902</v>
       </c>
       <c r="F23">
-        <v>53.361</v>
+        <v>55.902</v>
       </c>
       <c r="G23">
         <v>10.8</v>
@@ -3173,28 +3173,28 @@
         <v>19.2</v>
       </c>
       <c r="M23">
-        <v>2.8975023</v>
+        <v>3.0354786</v>
       </c>
       <c r="N23">
-        <v>16.3024977</v>
+        <v>16.1645214</v>
       </c>
       <c r="O23">
-        <v>3.097474563</v>
+        <v>3.071259066</v>
       </c>
       <c r="P23">
-        <v>13.205023137</v>
+        <v>13.093262334</v>
       </c>
       <c r="Q23">
-        <v>19.305023137</v>
+        <v>19.193262334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1051935630173538</v>
+        <v>0.1058359745455875</v>
       </c>
       <c r="T23">
-        <v>1.001460798548645</v>
+        <v>1.012292779816947</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.626396810798045</v>
+        <v>6.325196955761769</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09222832014555823</v>
+        <v>0.09230359550740694</v>
       </c>
       <c r="C24">
-        <v>210.6635748081058</v>
+        <v>207.7085671172584</v>
       </c>
       <c r="D24">
-        <v>255.7655748081058</v>
+        <v>255.3515671172584</v>
       </c>
       <c r="E24">
-        <v>31.902</v>
+        <v>34.443</v>
       </c>
       <c r="F24">
-        <v>55.902</v>
+        <v>58.443</v>
       </c>
       <c r="G24">
         <v>10.8</v>
@@ -3255,45 +3255,45 @@
         <v>19.2</v>
       </c>
       <c r="M24">
-        <v>3.0354786</v>
+        <v>3.2318979</v>
       </c>
       <c r="N24">
-        <v>16.1645214</v>
+        <v>15.9681021</v>
       </c>
       <c r="O24">
-        <v>3.071259066</v>
+        <v>3.033939399</v>
       </c>
       <c r="P24">
-        <v>13.093262334</v>
+        <v>12.934162701</v>
       </c>
       <c r="Q24">
-        <v>19.193262334</v>
+        <v>19.034162701</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1058359745455875</v>
+        <v>0.1064950720875415</v>
       </c>
       <c r="T24">
-        <v>1.012292779816947</v>
+        <v>1.023406111248063</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.325196955761769</v>
+        <v>5.940781730759502</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09230359550740694</v>
+        <v>0.09220067086925565</v>
       </c>
       <c r="C25">
-        <v>207.7085671172584</v>
+        <v>205.7339806443594</v>
       </c>
       <c r="D25">
-        <v>255.3515671172584</v>
+        <v>255.9179806443594</v>
       </c>
       <c r="E25">
-        <v>34.443</v>
+        <v>36.984</v>
       </c>
       <c r="F25">
-        <v>58.443</v>
+        <v>60.984</v>
       </c>
       <c r="G25">
         <v>10.8</v>
@@ -3337,28 +3337,28 @@
         <v>19.2</v>
       </c>
       <c r="M25">
-        <v>3.2318979</v>
+        <v>3.3724152</v>
       </c>
       <c r="N25">
-        <v>15.9681021</v>
+        <v>15.8275848</v>
       </c>
       <c r="O25">
-        <v>3.033939399</v>
+        <v>3.007241112</v>
       </c>
       <c r="P25">
-        <v>12.934162701</v>
+        <v>12.820343688</v>
       </c>
       <c r="Q25">
-        <v>19.034162701</v>
+        <v>18.920343688</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1064950720875415</v>
+        <v>0.1071715143016522</v>
       </c>
       <c r="T25">
-        <v>1.023406111248063</v>
+        <v>1.034811898769471</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.940781730759502</v>
+        <v>5.693249158644522</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09220067086925565</v>
+        <v>0.09209774623110437</v>
       </c>
       <c r="C26">
-        <v>205.7339806443594</v>
+        <v>203.7619125621842</v>
       </c>
       <c r="D26">
-        <v>255.9179806443594</v>
+        <v>256.4869125621842</v>
       </c>
       <c r="E26">
-        <v>36.98399999999999</v>
+        <v>39.525</v>
       </c>
       <c r="F26">
-        <v>60.98399999999999</v>
+        <v>63.525</v>
       </c>
       <c r="G26">
         <v>10.8</v>
@@ -3419,28 +3419,28 @@
         <v>19.2</v>
       </c>
       <c r="M26">
-        <v>3.3724152</v>
+        <v>3.5129325</v>
       </c>
       <c r="N26">
-        <v>15.8275848</v>
+        <v>15.6870675</v>
       </c>
       <c r="O26">
-        <v>3.007241112</v>
+        <v>2.980542825</v>
       </c>
       <c r="P26">
-        <v>12.820343688</v>
+        <v>12.706524675</v>
       </c>
       <c r="Q26">
-        <v>18.920343688</v>
+        <v>18.806524675</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1071715143016522</v>
+        <v>0.1078659949748058</v>
       </c>
       <c r="T26">
-        <v>1.034811898769471</v>
+        <v>1.046521840624784</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.693249158644523</v>
+        <v>5.465519192298742</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09209774623110437</v>
+        <v>0.09199482159295308</v>
       </c>
       <c r="C27">
-        <v>203.7619125621842</v>
+        <v>201.7923797040777</v>
       </c>
       <c r="D27">
-        <v>256.4869125621842</v>
+        <v>257.0583797040777</v>
       </c>
       <c r="E27">
-        <v>39.525</v>
+        <v>42.066</v>
       </c>
       <c r="F27">
-        <v>63.525</v>
+        <v>66.066</v>
       </c>
       <c r="G27">
         <v>10.8</v>
@@ -3501,28 +3501,28 @@
         <v>19.2</v>
       </c>
       <c r="M27">
-        <v>3.5129325</v>
+        <v>3.6534498</v>
       </c>
       <c r="N27">
-        <v>15.6870675</v>
+        <v>15.5465502</v>
       </c>
       <c r="O27">
-        <v>2.980542825</v>
+        <v>2.953844538</v>
       </c>
       <c r="P27">
-        <v>12.706524675</v>
+        <v>12.592705662</v>
       </c>
       <c r="Q27">
-        <v>18.806524675</v>
+        <v>18.692705662</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1078659949748058</v>
+        <v>0.1085792453958825</v>
       </c>
       <c r="T27">
-        <v>1.046521840624784</v>
+        <v>1.058548267395105</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.465519192298742</v>
+        <v>5.255306915671866</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09199482159295308</v>
+        <v>0.09189189695480179</v>
       </c>
       <c r="C28">
-        <v>201.7923797040777</v>
+        <v>199.8253990537422</v>
       </c>
       <c r="D28">
-        <v>257.0583797040777</v>
+        <v>257.6323990537422</v>
       </c>
       <c r="E28">
-        <v>42.066</v>
+        <v>44.607</v>
       </c>
       <c r="F28">
-        <v>66.066</v>
+        <v>68.607</v>
       </c>
       <c r="G28">
         <v>10.8</v>
@@ -3583,28 +3583,28 @@
         <v>19.2</v>
       </c>
       <c r="M28">
-        <v>3.6534498</v>
+        <v>3.7939671</v>
       </c>
       <c r="N28">
-        <v>15.5465502</v>
+        <v>15.4060329</v>
       </c>
       <c r="O28">
-        <v>2.953844538</v>
+        <v>2.927146251</v>
       </c>
       <c r="P28">
-        <v>12.592705662</v>
+        <v>12.478886649</v>
       </c>
       <c r="Q28">
-        <v>18.692705662</v>
+        <v>18.578886649</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1085792453958825</v>
+        <v>0.109312036924386</v>
       </c>
       <c r="T28">
-        <v>1.058548267395105</v>
+        <v>1.070904185309818</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.255306915671866</v>
+        <v>5.060665918795131</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09189189695480179</v>
+        <v>0.09178897231665049</v>
       </c>
       <c r="C29">
-        <v>199.8253990537422</v>
+        <v>197.8609877469202</v>
       </c>
       <c r="D29">
-        <v>257.6323990537422</v>
+        <v>258.2089877469202</v>
       </c>
       <c r="E29">
-        <v>44.607</v>
+        <v>47.14800000000001</v>
       </c>
       <c r="F29">
-        <v>68.607</v>
+        <v>71.14800000000001</v>
       </c>
       <c r="G29">
         <v>10.8</v>
@@ -3665,28 +3665,28 @@
         <v>19.2</v>
       </c>
       <c r="M29">
-        <v>3.7939671</v>
+        <v>3.934484400000001</v>
       </c>
       <c r="N29">
-        <v>15.4060329</v>
+        <v>15.2655156</v>
       </c>
       <c r="O29">
-        <v>2.927146251</v>
+        <v>2.900447964</v>
       </c>
       <c r="P29">
-        <v>12.478886649</v>
+        <v>12.365067636</v>
       </c>
       <c r="Q29">
-        <v>18.578886649</v>
+        <v>18.465067636</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.109312036924386</v>
+        <v>0.1100651837731257</v>
       </c>
       <c r="T29">
-        <v>1.070904185309818</v>
+        <v>1.083603323166607</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.060665918795131</v>
+        <v>4.879927850266733</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09178897231665049</v>
+        <v>0.09168604767849922</v>
       </c>
       <c r="C30">
-        <v>197.8609877469202</v>
+        <v>195.8991630730991</v>
       </c>
       <c r="D30">
-        <v>258.2089877469202</v>
+        <v>258.7881630730992</v>
       </c>
       <c r="E30">
-        <v>47.14800000000001</v>
+        <v>49.68900000000001</v>
       </c>
       <c r="F30">
-        <v>71.14800000000001</v>
+        <v>73.68900000000001</v>
       </c>
       <c r="G30">
         <v>10.8</v>
@@ -3747,28 +3747,28 @@
         <v>19.2</v>
       </c>
       <c r="M30">
-        <v>3.934484400000001</v>
+        <v>4.075001700000001</v>
       </c>
       <c r="N30">
-        <v>15.2655156</v>
+        <v>15.1249983</v>
       </c>
       <c r="O30">
-        <v>2.900447964</v>
+        <v>2.873749677</v>
       </c>
       <c r="P30">
-        <v>12.365067636</v>
+        <v>12.251248623</v>
       </c>
       <c r="Q30">
-        <v>18.465067636</v>
+        <v>18.351248623</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1100651837731257</v>
+        <v>0.1108395460260553</v>
       </c>
       <c r="T30">
-        <v>1.083603323166607</v>
+        <v>1.096660183216545</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.879927850266733</v>
+        <v>4.711654476119604</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09168604767849922</v>
+        <v>0.09158312304034792</v>
       </c>
       <c r="C31">
-        <v>195.8991630730992</v>
+        <v>193.9399424772404</v>
       </c>
       <c r="D31">
-        <v>258.7881630730992</v>
+        <v>259.3699424772404</v>
       </c>
       <c r="E31">
-        <v>49.68899999999999</v>
+        <v>52.22999999999999</v>
       </c>
       <c r="F31">
-        <v>73.68899999999999</v>
+        <v>76.22999999999999</v>
       </c>
       <c r="G31">
         <v>10.8</v>
@@ -3829,28 +3829,28 @@
         <v>19.2</v>
       </c>
       <c r="M31">
-        <v>4.0750017</v>
+        <v>4.215519</v>
       </c>
       <c r="N31">
-        <v>15.1249983</v>
+        <v>14.984481</v>
       </c>
       <c r="O31">
-        <v>2.873749677</v>
+        <v>2.84705139</v>
       </c>
       <c r="P31">
-        <v>12.251248623</v>
+        <v>12.13742961</v>
       </c>
       <c r="Q31">
-        <v>18.351248623</v>
+        <v>18.23742961</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1108395460260553</v>
+        <v>0.1116360329147827</v>
       </c>
       <c r="T31">
-        <v>1.096660183216545</v>
+        <v>1.110090096410766</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.711654476119605</v>
+        <v>4.554599326915618</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09158312304034792</v>
+        <v>0.09210794840219665</v>
       </c>
       <c r="C32">
-        <v>193.9399424772404</v>
+        <v>188.4594055594951</v>
       </c>
       <c r="D32">
-        <v>259.3699424772404</v>
+        <v>256.4304055594951</v>
       </c>
       <c r="E32">
-        <v>52.22999999999999</v>
+        <v>54.771</v>
       </c>
       <c r="F32">
-        <v>76.22999999999999</v>
+        <v>78.771</v>
       </c>
       <c r="G32">
         <v>10.8</v>
@@ -3911,45 +3911,45 @@
         <v>19.2</v>
       </c>
       <c r="M32">
-        <v>4.215519</v>
+        <v>4.552963800000001</v>
       </c>
       <c r="N32">
-        <v>14.984481</v>
+        <v>14.6470362</v>
       </c>
       <c r="O32">
-        <v>2.84705139</v>
+        <v>2.782936878</v>
       </c>
       <c r="P32">
-        <v>12.13742961</v>
+        <v>11.864099322</v>
       </c>
       <c r="Q32">
-        <v>18.23742961</v>
+        <v>17.964099322</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1116360329147827</v>
+        <v>0.1124556063799952</v>
       </c>
       <c r="T32">
-        <v>1.110090096410766</v>
+        <v>1.123909282451197</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.19</v>
       </c>
       <c r="W32">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.554599326915618</v>
+        <v>4.217033309160067</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09210794840219665</v>
+        <v>0.09202527376404536</v>
       </c>
       <c r="C33">
-        <v>188.4594055594951</v>
+        <v>186.3770354228645</v>
       </c>
       <c r="D33">
-        <v>256.4304055594951</v>
+        <v>256.8890354228645</v>
       </c>
       <c r="E33">
-        <v>54.771</v>
+        <v>57.312</v>
       </c>
       <c r="F33">
-        <v>78.771</v>
+        <v>81.312</v>
       </c>
       <c r="G33">
         <v>10.8</v>
@@ -3993,28 +3993,28 @@
         <v>19.2</v>
       </c>
       <c r="M33">
-        <v>4.552963800000001</v>
+        <v>4.6998336</v>
       </c>
       <c r="N33">
-        <v>14.6470362</v>
+        <v>14.5001664</v>
       </c>
       <c r="O33">
-        <v>2.782936878</v>
+        <v>2.755031616</v>
       </c>
       <c r="P33">
-        <v>11.864099322</v>
+        <v>11.745134784</v>
       </c>
       <c r="Q33">
-        <v>17.964099322</v>
+        <v>17.845134784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1124556063799952</v>
+        <v>0.1132992849471255</v>
       </c>
       <c r="T33">
-        <v>1.123909282451197</v>
+        <v>1.138134915139876</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.217033309160067</v>
+        <v>4.085251018248816</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09202527376404536</v>
+        <v>0.09287814912589407</v>
       </c>
       <c r="C34">
-        <v>186.3770354228645</v>
+        <v>179.1821921195658</v>
       </c>
       <c r="D34">
-        <v>256.8890354228645</v>
+        <v>252.2351921195658</v>
       </c>
       <c r="E34">
-        <v>57.312</v>
+        <v>59.85300000000001</v>
       </c>
       <c r="F34">
-        <v>81.312</v>
+        <v>83.85300000000001</v>
       </c>
       <c r="G34">
         <v>10.8</v>
@@ -4075,45 +4075,45 @@
         <v>19.2</v>
       </c>
       <c r="M34">
-        <v>4.6998336</v>
+        <v>5.140188900000001</v>
       </c>
       <c r="N34">
-        <v>14.5001664</v>
+        <v>14.0598111</v>
       </c>
       <c r="O34">
-        <v>2.755031616</v>
+        <v>2.671364109</v>
       </c>
       <c r="P34">
-        <v>11.745134784</v>
+        <v>11.388446991</v>
       </c>
       <c r="Q34">
-        <v>17.845134784</v>
+        <v>17.488446991</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1132992849471255</v>
+        <v>0.1141681479490956</v>
       </c>
       <c r="T34">
-        <v>1.138134915139876</v>
+        <v>1.152785193580456</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.085251018248816</v>
+        <v>3.73527128545801</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09287814912589407</v>
+        <v>0.09282382448774279</v>
       </c>
       <c r="C35">
-        <v>179.1821921195658</v>
+        <v>176.9325887826442</v>
       </c>
       <c r="D35">
-        <v>252.2351921195658</v>
+        <v>252.5265887826442</v>
       </c>
       <c r="E35">
-        <v>59.85300000000001</v>
+        <v>62.39400000000001</v>
       </c>
       <c r="F35">
-        <v>83.85300000000001</v>
+        <v>86.39400000000001</v>
       </c>
       <c r="G35">
         <v>10.8</v>
@@ -4157,28 +4157,28 @@
         <v>19.2</v>
       </c>
       <c r="M35">
-        <v>5.140188900000001</v>
+        <v>5.2959522</v>
       </c>
       <c r="N35">
-        <v>14.0598111</v>
+        <v>13.9040478</v>
       </c>
       <c r="O35">
-        <v>2.671364109</v>
+        <v>2.641769082</v>
       </c>
       <c r="P35">
-        <v>11.388446991</v>
+        <v>11.262278718</v>
       </c>
       <c r="Q35">
-        <v>17.488446991</v>
+        <v>17.362278718</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1141681479490956</v>
+        <v>0.1150633401329436</v>
       </c>
       <c r="T35">
-        <v>1.152785193580456</v>
+        <v>1.167879419852569</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.73527128545801</v>
+        <v>3.625410365297481</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09282382448774279</v>
+        <v>0.09276949984959151</v>
       </c>
       <c r="C36">
-        <v>176.9325887826442</v>
+        <v>174.6836595009428</v>
       </c>
       <c r="D36">
-        <v>252.5265887826442</v>
+        <v>252.8186595009428</v>
       </c>
       <c r="E36">
-        <v>62.39400000000001</v>
+        <v>64.935</v>
       </c>
       <c r="F36">
-        <v>86.39400000000001</v>
+        <v>88.935</v>
       </c>
       <c r="G36">
         <v>10.8</v>
@@ -4239,28 +4239,28 @@
         <v>19.2</v>
       </c>
       <c r="M36">
-        <v>5.2959522</v>
+        <v>5.451715500000001</v>
       </c>
       <c r="N36">
-        <v>13.9040478</v>
+        <v>13.7482845</v>
       </c>
       <c r="O36">
-        <v>2.641769082</v>
+        <v>2.612174055</v>
       </c>
       <c r="P36">
-        <v>11.262278718</v>
+        <v>11.136110445</v>
       </c>
       <c r="Q36">
-        <v>17.362278718</v>
+        <v>17.236110445</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1150633401329436</v>
+        <v>0.1159860766916793</v>
       </c>
       <c r="T36">
-        <v>1.167879419852569</v>
+        <v>1.183438083856131</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.625410365297481</v>
+        <v>3.521827212003267</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09276949984959151</v>
+        <v>0.09353165521144022</v>
       </c>
       <c r="C37">
-        <v>174.6836595009428</v>
+        <v>168.1057767224075</v>
       </c>
       <c r="D37">
-        <v>252.8186595009428</v>
+        <v>248.7817767224075</v>
       </c>
       <c r="E37">
-        <v>64.935</v>
+        <v>67.47600000000001</v>
       </c>
       <c r="F37">
-        <v>88.935</v>
+        <v>91.47600000000001</v>
       </c>
       <c r="G37">
         <v>10.8</v>
@@ -4321,45 +4321,45 @@
         <v>19.2</v>
       </c>
       <c r="M37">
-        <v>5.451715500000001</v>
+        <v>5.863611600000001</v>
       </c>
       <c r="N37">
-        <v>13.7482845</v>
+        <v>13.3363884</v>
       </c>
       <c r="O37">
-        <v>2.612174055</v>
+        <v>2.533913795999999</v>
       </c>
       <c r="P37">
-        <v>11.136110445</v>
+        <v>10.802474604</v>
       </c>
       <c r="Q37">
-        <v>17.236110445</v>
+        <v>16.902474604</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1159860766916793</v>
+        <v>0.1169376487678754</v>
       </c>
       <c r="T37">
-        <v>1.183438083856131</v>
+        <v>1.199482956109804</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.19</v>
       </c>
       <c r="W37">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.521827212003267</v>
+        <v>3.274432433416973</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09353165521144022</v>
+        <v>0.09350001057328894</v>
       </c>
       <c r="C38">
-        <v>168.1057767224075</v>
+        <v>165.7298209060124</v>
       </c>
       <c r="D38">
-        <v>248.7817767224075</v>
+        <v>248.9468209060124</v>
       </c>
       <c r="E38">
-        <v>67.476</v>
+        <v>70.017</v>
       </c>
       <c r="F38">
-        <v>91.476</v>
+        <v>94.017</v>
       </c>
       <c r="G38">
         <v>10.8</v>
@@ -4403,28 +4403,28 @@
         <v>19.2</v>
       </c>
       <c r="M38">
-        <v>5.8636116</v>
+        <v>6.0264897</v>
       </c>
       <c r="N38">
-        <v>13.3363884</v>
+        <v>13.1735103</v>
       </c>
       <c r="O38">
-        <v>2.533913796</v>
+        <v>2.502966957</v>
       </c>
       <c r="P38">
-        <v>10.802474604</v>
+        <v>10.670543343</v>
       </c>
       <c r="Q38">
-        <v>16.902474604</v>
+        <v>16.770543343</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1169376487678754</v>
+        <v>0.117919429481411</v>
       </c>
       <c r="T38">
-        <v>1.199482956109804</v>
+        <v>1.216037189387404</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.274432433416974</v>
+        <v>3.18593425954084</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09350001057328894</v>
+        <v>0.09346836593513767</v>
       </c>
       <c r="C39">
-        <v>165.7298209060124</v>
+        <v>163.3540842187343</v>
       </c>
       <c r="D39">
-        <v>248.9468209060124</v>
+        <v>249.1120842187343</v>
       </c>
       <c r="E39">
-        <v>70.017</v>
+        <v>72.55799999999999</v>
       </c>
       <c r="F39">
-        <v>94.017</v>
+        <v>96.55799999999999</v>
       </c>
       <c r="G39">
         <v>10.8</v>
@@ -4485,28 +4485,28 @@
         <v>19.2</v>
       </c>
       <c r="M39">
-        <v>6.0264897</v>
+        <v>6.1893678</v>
       </c>
       <c r="N39">
-        <v>13.1735103</v>
+        <v>13.0106322</v>
       </c>
       <c r="O39">
-        <v>2.502966957</v>
+        <v>2.472020118</v>
       </c>
       <c r="P39">
-        <v>10.670543343</v>
+        <v>10.538612082</v>
       </c>
       <c r="Q39">
-        <v>16.770543343</v>
+        <v>16.638612082</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.117919429481411</v>
+        <v>0.1189328805405446</v>
       </c>
       <c r="T39">
-        <v>1.216037189387404</v>
+        <v>1.233125430190087</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.18593425954084</v>
+        <v>3.102093884289765</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09346836593513767</v>
+        <v>0.09343672129698638</v>
       </c>
       <c r="C40">
-        <v>163.3540842187343</v>
+        <v>160.9785670972697</v>
       </c>
       <c r="D40">
-        <v>249.1120842187343</v>
+        <v>249.2775670972697</v>
       </c>
       <c r="E40">
-        <v>72.55799999999999</v>
+        <v>75.099</v>
       </c>
       <c r="F40">
-        <v>96.55799999999999</v>
+        <v>99.099</v>
       </c>
       <c r="G40">
         <v>10.8</v>
@@ -4567,28 +4567,28 @@
         <v>19.2</v>
       </c>
       <c r="M40">
-        <v>6.1893678</v>
+        <v>6.352245900000001</v>
       </c>
       <c r="N40">
-        <v>13.0106322</v>
+        <v>12.8477541</v>
       </c>
       <c r="O40">
-        <v>2.472020118</v>
+        <v>2.441073279</v>
       </c>
       <c r="P40">
-        <v>10.538612082</v>
+        <v>10.406680821</v>
       </c>
       <c r="Q40">
-        <v>16.638612082</v>
+        <v>16.506680821</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1189328805405446</v>
+        <v>0.1199795595032564</v>
       </c>
       <c r="T40">
-        <v>1.233125430190087</v>
+        <v>1.250773941183023</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.102093884289765</v>
+        <v>3.022553015461822</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09343672129698638</v>
+        <v>0.09593227665883509</v>
       </c>
       <c r="C41">
-        <v>160.9785670972697</v>
+        <v>146.028675847593</v>
       </c>
       <c r="D41">
-        <v>249.2775670972697</v>
+        <v>236.868675847593</v>
       </c>
       <c r="E41">
-        <v>75.099</v>
+        <v>77.64</v>
       </c>
       <c r="F41">
-        <v>99.099</v>
+        <v>101.64</v>
       </c>
       <c r="G41">
         <v>10.8</v>
@@ -4649,45 +4649,45 @@
         <v>19.2</v>
       </c>
       <c r="M41">
-        <v>6.352245900000001</v>
+        <v>7.307916000000001</v>
       </c>
       <c r="N41">
-        <v>12.8477541</v>
+        <v>11.892084</v>
       </c>
       <c r="O41">
-        <v>2.441073279</v>
+        <v>2.25949596</v>
       </c>
       <c r="P41">
-        <v>10.406680821</v>
+        <v>9.632588039999998</v>
       </c>
       <c r="Q41">
-        <v>16.506680821</v>
+        <v>15.73258804</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1199795595032564</v>
+        <v>0.1210611277647252</v>
       </c>
       <c r="T41">
-        <v>1.250773941183023</v>
+        <v>1.269010735875722</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.19</v>
       </c>
       <c r="W41">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.022553015461822</v>
+        <v>2.627287998384218</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09593227665883509</v>
+        <v>0.09596381202068381</v>
       </c>
       <c r="C42">
-        <v>146.028675847593</v>
+        <v>143.3387689144356</v>
       </c>
       <c r="D42">
-        <v>236.868675847593</v>
+        <v>236.7197689144356</v>
       </c>
       <c r="E42">
-        <v>77.64</v>
+        <v>80.18100000000001</v>
       </c>
       <c r="F42">
-        <v>101.64</v>
+        <v>104.181</v>
       </c>
       <c r="G42">
         <v>10.8</v>
@@ -4731,28 +4731,28 @@
         <v>19.2</v>
       </c>
       <c r="M42">
-        <v>7.307916000000001</v>
+        <v>7.490613900000001</v>
       </c>
       <c r="N42">
-        <v>11.892084</v>
+        <v>11.7093861</v>
       </c>
       <c r="O42">
-        <v>2.25949596</v>
+        <v>2.224783358999999</v>
       </c>
       <c r="P42">
-        <v>9.632588039999998</v>
+        <v>9.484602740999998</v>
       </c>
       <c r="Q42">
-        <v>15.73258804</v>
+        <v>15.584602741</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1210611277647252</v>
+        <v>0.1221793593570912</v>
       </c>
       <c r="T42">
-        <v>1.269010735875722</v>
+        <v>1.287865726998683</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.627287998384218</v>
+        <v>2.563207803301675</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09596381202068381</v>
+        <v>0.09599534738253253</v>
       </c>
       <c r="C43">
-        <v>143.3387689144356</v>
+        <v>140.6490490836399</v>
       </c>
       <c r="D43">
-        <v>236.7197689144356</v>
+        <v>236.5710490836399</v>
       </c>
       <c r="E43">
-        <v>80.18100000000001</v>
+        <v>82.72200000000001</v>
       </c>
       <c r="F43">
-        <v>104.181</v>
+        <v>106.722</v>
       </c>
       <c r="G43">
         <v>10.8</v>
@@ -4813,28 +4813,28 @@
         <v>19.2</v>
       </c>
       <c r="M43">
-        <v>7.490613900000001</v>
+        <v>7.673311800000001</v>
       </c>
       <c r="N43">
-        <v>11.7093861</v>
+        <v>11.5266882</v>
       </c>
       <c r="O43">
-        <v>2.224783358999999</v>
+        <v>2.190070758</v>
       </c>
       <c r="P43">
-        <v>9.484602740999998</v>
+        <v>9.336617442</v>
       </c>
       <c r="Q43">
-        <v>15.584602741</v>
+        <v>15.436617442</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1221793593570912</v>
+        <v>0.1233361506595388</v>
       </c>
       <c r="T43">
-        <v>1.287865726998683</v>
+        <v>1.307370890229332</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.563207803301675</v>
+        <v>2.502179046080207</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09599534738253254</v>
+        <v>0.09738525274438124</v>
       </c>
       <c r="C44">
-        <v>140.6490490836399</v>
+        <v>131.7339139948991</v>
       </c>
       <c r="D44">
-        <v>236.5710490836399</v>
+        <v>230.1969139948991</v>
       </c>
       <c r="E44">
-        <v>82.72199999999999</v>
+        <v>85.26299999999999</v>
       </c>
       <c r="F44">
-        <v>106.722</v>
+        <v>109.263</v>
       </c>
       <c r="G44">
         <v>10.8</v>
@@ -4895,45 +4895,45 @@
         <v>19.2</v>
       </c>
       <c r="M44">
-        <v>7.6733118</v>
+        <v>8.2821354</v>
       </c>
       <c r="N44">
-        <v>11.5266882</v>
+        <v>10.9178646</v>
       </c>
       <c r="O44">
-        <v>2.190070758</v>
+        <v>2.074394274</v>
       </c>
       <c r="P44">
-        <v>9.336617442</v>
+        <v>8.843470326</v>
       </c>
       <c r="Q44">
-        <v>15.436617442</v>
+        <v>14.943470326</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1233361506595388</v>
+        <v>0.1245335311304934</v>
       </c>
       <c r="T44">
-        <v>1.307370890229332</v>
+        <v>1.327560445152285</v>
       </c>
       <c r="U44">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.19</v>
       </c>
       <c r="W44">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.502179046080207</v>
+        <v>2.318242708275453</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09738525274438124</v>
+        <v>0.09744837810622997</v>
       </c>
       <c r="C45">
-        <v>131.7339139948991</v>
+        <v>128.9115641437479</v>
       </c>
       <c r="D45">
-        <v>230.1969139948991</v>
+        <v>229.9155641437479</v>
       </c>
       <c r="E45">
-        <v>85.26299999999999</v>
+        <v>87.804</v>
       </c>
       <c r="F45">
-        <v>109.263</v>
+        <v>111.804</v>
       </c>
       <c r="G45">
         <v>10.8</v>
@@ -4977,28 +4977,28 @@
         <v>19.2</v>
       </c>
       <c r="M45">
-        <v>8.2821354</v>
+        <v>8.474743200000001</v>
       </c>
       <c r="N45">
-        <v>10.9178646</v>
+        <v>10.7252568</v>
       </c>
       <c r="O45">
-        <v>2.074394274</v>
+        <v>2.037798792</v>
       </c>
       <c r="P45">
-        <v>8.843470326</v>
+        <v>8.687458007999998</v>
       </c>
       <c r="Q45">
-        <v>14.943470326</v>
+        <v>14.787458008</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1245335311304934</v>
+        <v>0.1257736751896964</v>
       </c>
       <c r="T45">
-        <v>1.327560445152285</v>
+        <v>1.3484710556082</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.318242708275453</v>
+        <v>2.265555373996465</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09744837810622997</v>
+        <v>0.09751150346807869</v>
       </c>
       <c r="C46">
-        <v>128.9115641437479</v>
+        <v>126.0899011924147</v>
       </c>
       <c r="D46">
-        <v>229.9155641437479</v>
+        <v>229.6349011924147</v>
       </c>
       <c r="E46">
-        <v>87.804</v>
+        <v>90.345</v>
       </c>
       <c r="F46">
-        <v>111.804</v>
+        <v>114.345</v>
       </c>
       <c r="G46">
         <v>10.8</v>
@@ -5059,28 +5059,28 @@
         <v>19.2</v>
       </c>
       <c r="M46">
-        <v>8.474743200000001</v>
+        <v>8.667351</v>
       </c>
       <c r="N46">
-        <v>10.7252568</v>
+        <v>10.532649</v>
       </c>
       <c r="O46">
-        <v>2.037798792</v>
+        <v>2.00120331</v>
       </c>
       <c r="P46">
-        <v>8.687458007999998</v>
+        <v>8.53144569</v>
       </c>
       <c r="Q46">
-        <v>14.787458008</v>
+        <v>14.63144569</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1257736751896964</v>
+        <v>0.1270589153965067</v>
       </c>
       <c r="T46">
-        <v>1.3484710556082</v>
+        <v>1.370142051898876</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.265555373996465</v>
+        <v>2.215209699018766</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09751150346807869</v>
+        <v>0.09757462882992739</v>
       </c>
       <c r="C47">
-        <v>126.0899011924147</v>
+        <v>123.2689226284258</v>
       </c>
       <c r="D47">
-        <v>229.6349011924147</v>
+        <v>229.3549226284258</v>
       </c>
       <c r="E47">
-        <v>90.345</v>
+        <v>92.886</v>
       </c>
       <c r="F47">
-        <v>114.345</v>
+        <v>116.886</v>
       </c>
       <c r="G47">
         <v>10.8</v>
@@ -5141,28 +5141,28 @@
         <v>19.2</v>
       </c>
       <c r="M47">
-        <v>8.667351</v>
+        <v>8.859958800000001</v>
       </c>
       <c r="N47">
-        <v>10.532649</v>
+        <v>10.3400412</v>
       </c>
       <c r="O47">
-        <v>2.00120331</v>
+        <v>1.964607828</v>
       </c>
       <c r="P47">
-        <v>8.53144569</v>
+        <v>8.375433371999998</v>
       </c>
       <c r="Q47">
-        <v>14.63144569</v>
+        <v>14.475433372</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1270589153965067</v>
+        <v>0.1283917570924581</v>
       </c>
       <c r="T47">
-        <v>1.370142051898876</v>
+        <v>1.392615677681799</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.215209699018766</v>
+        <v>2.167052966431401</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09757462882992739</v>
+        <v>0.09763775419177612</v>
       </c>
       <c r="C48">
-        <v>123.2689226284258</v>
+        <v>120.4486259515454</v>
       </c>
       <c r="D48">
-        <v>229.3549226284258</v>
+        <v>229.0756259515454</v>
       </c>
       <c r="E48">
-        <v>92.886</v>
+        <v>95.42700000000001</v>
       </c>
       <c r="F48">
-        <v>116.886</v>
+        <v>119.427</v>
       </c>
       <c r="G48">
         <v>10.8</v>
@@ -5223,28 +5223,28 @@
         <v>19.2</v>
       </c>
       <c r="M48">
-        <v>8.859958800000001</v>
+        <v>9.0525666</v>
       </c>
       <c r="N48">
-        <v>10.3400412</v>
+        <v>10.1474334</v>
       </c>
       <c r="O48">
-        <v>1.964607828</v>
+        <v>1.928012346</v>
       </c>
       <c r="P48">
-        <v>8.375433371999998</v>
+        <v>8.219421054</v>
       </c>
       <c r="Q48">
-        <v>14.475433372</v>
+        <v>14.319421054</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1283917570924581</v>
+        <v>0.1297748947014644</v>
       </c>
       <c r="T48">
-        <v>1.392615677681799</v>
+        <v>1.415937364815021</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.167052966431401</v>
+        <v>2.120945456507329</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09763775419177612</v>
+        <v>0.09770087955362483</v>
       </c>
       <c r="C49">
-        <v>120.4486259515454</v>
+        <v>117.629008673702</v>
       </c>
       <c r="D49">
-        <v>229.0756259515454</v>
+        <v>228.797008673702</v>
       </c>
       <c r="E49">
-        <v>95.42700000000001</v>
+        <v>97.968</v>
       </c>
       <c r="F49">
-        <v>119.427</v>
+        <v>121.968</v>
       </c>
       <c r="G49">
         <v>10.8</v>
@@ -5305,28 +5305,28 @@
         <v>19.2</v>
       </c>
       <c r="M49">
-        <v>9.0525666</v>
+        <v>9.245174400000002</v>
       </c>
       <c r="N49">
-        <v>10.1474334</v>
+        <v>9.954825599999998</v>
       </c>
       <c r="O49">
-        <v>1.928012346</v>
+        <v>1.891416864</v>
       </c>
       <c r="P49">
-        <v>8.219421054</v>
+        <v>8.063408735999998</v>
       </c>
       <c r="Q49">
-        <v>14.319421054</v>
+        <v>14.163408736</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1297748947014644</v>
+        <v>0.131211229910817</v>
       </c>
       <c r="T49">
-        <v>1.415937364815021</v>
+        <v>1.440156039914906</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.120945456507329</v>
+        <v>2.076759092830093</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09770087955362483</v>
+        <v>0.09776400491547353</v>
       </c>
       <c r="C50">
-        <v>117.629008673702</v>
+        <v>114.8100683189137</v>
       </c>
       <c r="D50">
-        <v>228.797008673702</v>
+        <v>228.5190683189136</v>
       </c>
       <c r="E50">
-        <v>97.96799999999999</v>
+        <v>100.509</v>
       </c>
       <c r="F50">
-        <v>121.968</v>
+        <v>124.509</v>
       </c>
       <c r="G50">
         <v>10.8</v>
@@ -5387,28 +5387,28 @@
         <v>19.2</v>
       </c>
       <c r="M50">
-        <v>9.2451744</v>
+        <v>9.437782200000001</v>
       </c>
       <c r="N50">
-        <v>9.954825599999999</v>
+        <v>9.762217799999998</v>
       </c>
       <c r="O50">
-        <v>1.891416864</v>
+        <v>1.854821382</v>
       </c>
       <c r="P50">
-        <v>8.063408736</v>
+        <v>7.907396417999998</v>
       </c>
       <c r="Q50">
-        <v>14.163408736</v>
+        <v>14.007396418</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.131211229910817</v>
+        <v>0.1327038919911246</v>
       </c>
       <c r="T50">
-        <v>1.440156039914906</v>
+        <v>1.465324466979491</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.076759092830093</v>
+        <v>2.034376254200907</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09776400491547353</v>
+        <v>0.1035781302773222</v>
       </c>
       <c r="C51">
-        <v>114.8100683189137</v>
+        <v>89.27354208083945</v>
       </c>
       <c r="D51">
-        <v>228.5190683189136</v>
+        <v>205.5235420808394</v>
       </c>
       <c r="E51">
-        <v>100.509</v>
+        <v>103.05</v>
       </c>
       <c r="F51">
-        <v>124.509</v>
+        <v>127.05</v>
       </c>
       <c r="G51">
         <v>10.8</v>
@@ -5469,45 +5469,45 @@
         <v>19.2</v>
       </c>
       <c r="M51">
-        <v>9.437782200000001</v>
+        <v>11.4345</v>
       </c>
       <c r="N51">
-        <v>9.762217799999998</v>
+        <v>7.765499999999999</v>
       </c>
       <c r="O51">
-        <v>1.854821382</v>
+        <v>1.475445</v>
       </c>
       <c r="P51">
-        <v>7.907396417999998</v>
+        <v>6.290055</v>
       </c>
       <c r="Q51">
-        <v>14.007396418</v>
+        <v>12.390055</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1327038919911246</v>
+        <v>0.1342562605546445</v>
       </c>
       <c r="T51">
-        <v>1.465324466979491</v>
+        <v>1.491499631126661</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.034376254200907</v>
+        <v>1.679128951856224</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1035781302773222</v>
+        <v>0.103756275639171</v>
       </c>
       <c r="C52">
-        <v>89.27354208083945</v>
+        <v>86.10080608040397</v>
       </c>
       <c r="D52">
-        <v>205.5235420808394</v>
+        <v>204.891806080404</v>
       </c>
       <c r="E52">
-        <v>103.05</v>
+        <v>105.591</v>
       </c>
       <c r="F52">
-        <v>127.05</v>
+        <v>129.591</v>
       </c>
       <c r="G52">
         <v>10.8</v>
@@ -5551,28 +5551,28 @@
         <v>19.2</v>
       </c>
       <c r="M52">
-        <v>11.4345</v>
+        <v>11.66319</v>
       </c>
       <c r="N52">
-        <v>7.765499999999999</v>
+        <v>7.536809999999999</v>
       </c>
       <c r="O52">
-        <v>1.475445</v>
+        <v>1.4319939</v>
       </c>
       <c r="P52">
-        <v>6.290055</v>
+        <v>6.104816099999999</v>
       </c>
       <c r="Q52">
-        <v>12.390055</v>
+        <v>12.2048161</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1342562605546445</v>
+        <v>0.1358719911003489</v>
       </c>
       <c r="T52">
-        <v>1.491499631126661</v>
+        <v>1.518743169320653</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.679128951856224</v>
+        <v>1.646204854761004</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.103756275639171</v>
+        <v>0.1039344210010197</v>
       </c>
       <c r="C53">
-        <v>86.10080608040397</v>
+        <v>82.93194182536325</v>
       </c>
       <c r="D53">
-        <v>204.891806080404</v>
+        <v>204.2639418253632</v>
       </c>
       <c r="E53">
-        <v>105.591</v>
+        <v>108.132</v>
       </c>
       <c r="F53">
-        <v>129.591</v>
+        <v>132.132</v>
       </c>
       <c r="G53">
         <v>10.8</v>
@@ -5633,28 +5633,28 @@
         <v>19.2</v>
       </c>
       <c r="M53">
-        <v>11.66319</v>
+        <v>11.89188</v>
       </c>
       <c r="N53">
-        <v>7.536809999999999</v>
+        <v>7.308119999999999</v>
       </c>
       <c r="O53">
-        <v>1.4319939</v>
+        <v>1.3885428</v>
       </c>
       <c r="P53">
-        <v>6.104816099999999</v>
+        <v>5.919577199999999</v>
       </c>
       <c r="Q53">
-        <v>12.2048161</v>
+        <v>12.0195772</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1358719911003489</v>
+        <v>0.1375550437521243</v>
       </c>
       <c r="T53">
-        <v>1.518743169320653</v>
+        <v>1.547121854939395</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.646204854761004</v>
+        <v>1.614547069092524</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1039344210010197</v>
+        <v>0.1041125663628684</v>
       </c>
       <c r="C54">
-        <v>82.93194182536325</v>
+        <v>79.76691383107664</v>
       </c>
       <c r="D54">
-        <v>204.2639418253632</v>
+        <v>203.6399138310766</v>
       </c>
       <c r="E54">
-        <v>108.132</v>
+        <v>110.673</v>
       </c>
       <c r="F54">
-        <v>132.132</v>
+        <v>134.673</v>
       </c>
       <c r="G54">
         <v>10.8</v>
@@ -5715,28 +5715,28 @@
         <v>19.2</v>
       </c>
       <c r="M54">
-        <v>11.89188</v>
+        <v>12.12057</v>
       </c>
       <c r="N54">
-        <v>7.308119999999999</v>
+        <v>7.07943</v>
       </c>
       <c r="O54">
-        <v>1.3885428</v>
+        <v>1.3450917</v>
       </c>
       <c r="P54">
-        <v>5.919577199999999</v>
+        <v>5.7343383</v>
       </c>
       <c r="Q54">
-        <v>12.0195772</v>
+        <v>11.8343383</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1375550437521243</v>
+        <v>0.1393097156656775</v>
       </c>
       <c r="T54">
-        <v>1.547121854939395</v>
+        <v>1.576708144201488</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.614547069092524</v>
+        <v>1.584083916845495</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1041125663628684</v>
+        <v>0.1042907117247171</v>
       </c>
       <c r="C55">
-        <v>79.76691383107664</v>
+        <v>76.60568704520645</v>
       </c>
       <c r="D55">
-        <v>203.6399138310766</v>
+        <v>203.0196870452064</v>
       </c>
       <c r="E55">
-        <v>110.673</v>
+        <v>113.214</v>
       </c>
       <c r="F55">
-        <v>134.673</v>
+        <v>137.214</v>
       </c>
       <c r="G55">
         <v>10.8</v>
@@ -5797,28 +5797,28 @@
         <v>19.2</v>
       </c>
       <c r="M55">
-        <v>12.12057</v>
+        <v>12.34926</v>
       </c>
       <c r="N55">
-        <v>7.07943</v>
+        <v>6.85074</v>
       </c>
       <c r="O55">
-        <v>1.3450917</v>
+        <v>1.3016406</v>
       </c>
       <c r="P55">
-        <v>5.7343383</v>
+        <v>5.5490994</v>
       </c>
       <c r="Q55">
-        <v>11.8343383</v>
+        <v>11.6490994</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1393097156656775</v>
+        <v>0.1411406776624285</v>
       </c>
       <c r="T55">
-        <v>1.576708144201488</v>
+        <v>1.607580793866281</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.584083916845495</v>
+        <v>1.554749029496504</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1042907117247171</v>
+        <v>0.1044688570865658</v>
       </c>
       <c r="C56">
-        <v>76.60568704520645</v>
+        <v>73.44822684115456</v>
       </c>
       <c r="D56">
-        <v>203.0196870452064</v>
+        <v>202.4032268411545</v>
       </c>
       <c r="E56">
-        <v>113.214</v>
+        <v>115.755</v>
       </c>
       <c r="F56">
-        <v>137.214</v>
+        <v>139.755</v>
       </c>
       <c r="G56">
         <v>10.8</v>
@@ -5879,28 +5879,28 @@
         <v>19.2</v>
       </c>
       <c r="M56">
-        <v>12.34926</v>
+        <v>12.57795</v>
       </c>
       <c r="N56">
-        <v>6.85074</v>
+        <v>6.62205</v>
       </c>
       <c r="O56">
-        <v>1.3016406</v>
+        <v>1.2581895</v>
       </c>
       <c r="P56">
-        <v>5.5490994</v>
+        <v>5.363860499999999</v>
       </c>
       <c r="Q56">
-        <v>11.6490994</v>
+        <v>11.4638605</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1411406776624285</v>
+        <v>0.1430530157479241</v>
       </c>
       <c r="T56">
-        <v>1.607580793866281</v>
+        <v>1.639825561293953</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.554749029496504</v>
+        <v>1.52648086532384</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1044688570865658</v>
+        <v>0.132094901604603</v>
       </c>
       <c r="C57">
-        <v>73.44822684115456</v>
+        <v>6.110808381482173</v>
       </c>
       <c r="D57">
-        <v>202.4032268411545</v>
+        <v>137.6068083814822</v>
       </c>
       <c r="E57">
-        <v>115.755</v>
+        <v>118.296</v>
       </c>
       <c r="F57">
-        <v>139.755</v>
+        <v>142.296</v>
       </c>
       <c r="G57">
         <v>10.8</v>
@@ -5961,45 +5961,45 @@
         <v>19.2</v>
       </c>
       <c r="M57">
-        <v>12.57795</v>
+        <v>20.88905280000001</v>
       </c>
       <c r="N57">
-        <v>6.62205</v>
+        <v>-1.689052800000006</v>
       </c>
       <c r="O57">
-        <v>1.2581895</v>
+        <v>-0.3209200320000011</v>
       </c>
       <c r="P57">
-        <v>5.363860499999999</v>
+        <v>-1.368132768000005</v>
       </c>
       <c r="Q57">
-        <v>11.4638605</v>
+        <v>4.731867231999996</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1430530157479241</v>
+        <v>0.1460078503249402</v>
       </c>
       <c r="T57">
-        <v>1.639825561293953</v>
+        <v>1.689648317241648</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.19</v>
+        <v>0.1746369275298112</v>
       </c>
       <c r="W57">
-        <v>0.07290000000000001</v>
+        <v>0.1211632990386237</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.52648086532384</v>
+        <v>0.9191417238411114</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.132094901604603</v>
+        <v>0.133104901604603</v>
       </c>
       <c r="C58">
-        <v>6.110808381482173</v>
+        <v>1.97788314119336</v>
       </c>
       <c r="D58">
-        <v>137.6068083814822</v>
+        <v>136.0148831411934</v>
       </c>
       <c r="E58">
-        <v>118.296</v>
+        <v>120.837</v>
       </c>
       <c r="F58">
-        <v>142.296</v>
+        <v>144.837</v>
       </c>
       <c r="G58">
         <v>10.8</v>
@@ -6043,37 +6043,37 @@
         <v>19.2</v>
       </c>
       <c r="M58">
-        <v>20.88905280000001</v>
+        <v>21.26207160000001</v>
       </c>
       <c r="N58">
-        <v>-1.689052800000006</v>
+        <v>-2.062071600000007</v>
       </c>
       <c r="O58">
-        <v>-0.3209200320000011</v>
+        <v>-0.3917936040000012</v>
       </c>
       <c r="P58">
-        <v>-1.368132768000005</v>
+        <v>-1.670277996000005</v>
       </c>
       <c r="Q58">
-        <v>4.731867231999996</v>
+        <v>4.429722003999996</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1460078503249402</v>
+        <v>0.148338265448776</v>
       </c>
       <c r="T58">
-        <v>1.689648317241648</v>
+        <v>1.728942464154245</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1746369275298112</v>
+        <v>0.1715731217836741</v>
       </c>
       <c r="W58">
-        <v>0.1211632990386237</v>
+        <v>0.1216130657221566</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9191417238411114</v>
+        <v>0.9030164304403901</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.133104901604603</v>
+        <v>0.134114901604603</v>
       </c>
       <c r="C59">
-        <v>1.97788314119336</v>
+        <v>-2.118630475157062</v>
       </c>
       <c r="D59">
-        <v>136.0148831411934</v>
+        <v>134.4593695248429</v>
       </c>
       <c r="E59">
-        <v>120.837</v>
+        <v>123.378</v>
       </c>
       <c r="F59">
-        <v>144.837</v>
+        <v>147.378</v>
       </c>
       <c r="G59">
         <v>10.8</v>
@@ -6125,37 +6125,37 @@
         <v>19.2</v>
       </c>
       <c r="M59">
-        <v>21.26207160000001</v>
+        <v>21.6350904</v>
       </c>
       <c r="N59">
-        <v>-2.062071600000007</v>
+        <v>-2.435090400000004</v>
       </c>
       <c r="O59">
-        <v>-0.3917936040000012</v>
+        <v>-0.4626671760000007</v>
       </c>
       <c r="P59">
-        <v>-1.670277996000005</v>
+        <v>-1.972423224000003</v>
       </c>
       <c r="Q59">
-        <v>4.429722003999996</v>
+        <v>4.127576775999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.148338265448776</v>
+        <v>0.1507796527213659</v>
       </c>
       <c r="T59">
-        <v>1.728942464154245</v>
+        <v>1.770107760919822</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1715731217836741</v>
+        <v>0.1686149645115418</v>
       </c>
       <c r="W59">
-        <v>0.1216130657221566</v>
+        <v>0.1220473232097057</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9030164304403901</v>
+        <v>0.8874471816396938</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1341149016046029</v>
+        <v>0.1351249016046029</v>
       </c>
       <c r="C60">
-        <v>-2.118630475156948</v>
+        <v>-6.179967590346052</v>
       </c>
       <c r="D60">
-        <v>134.459369524843</v>
+        <v>132.9390324096539</v>
       </c>
       <c r="E60">
-        <v>123.378</v>
+        <v>125.919</v>
       </c>
       <c r="F60">
-        <v>147.378</v>
+        <v>149.919</v>
       </c>
       <c r="G60">
         <v>10.8</v>
@@ -6207,37 +6207,37 @@
         <v>19.2</v>
       </c>
       <c r="M60">
-        <v>21.6350904</v>
+        <v>22.0081092</v>
       </c>
       <c r="N60">
-        <v>-2.4350904</v>
+        <v>-2.808109200000001</v>
       </c>
       <c r="O60">
-        <v>-0.462667176</v>
+        <v>-0.5335407480000001</v>
       </c>
       <c r="P60">
-        <v>-1.972423224</v>
+        <v>-2.274568452</v>
       </c>
       <c r="Q60">
-        <v>4.127576776000002</v>
+        <v>3.825431548000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1507796527213659</v>
+        <v>0.1533401320560333</v>
       </c>
       <c r="T60">
-        <v>1.770107760919822</v>
+        <v>1.813281120942257</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1686149645115419</v>
+        <v>0.1657570837571089</v>
       </c>
       <c r="W60">
-        <v>0.1220473232097057</v>
+        <v>0.1224668601044564</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.887447181639694</v>
+        <v>0.8724057039847839</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1351249016046029</v>
+        <v>0.136134901604603</v>
       </c>
       <c r="C61">
-        <v>-6.179967590346052</v>
+        <v>-10.2073080894086</v>
       </c>
       <c r="D61">
-        <v>132.9390324096539</v>
+        <v>131.4526919105914</v>
       </c>
       <c r="E61">
-        <v>125.919</v>
+        <v>128.46</v>
       </c>
       <c r="F61">
-        <v>149.919</v>
+        <v>152.46</v>
       </c>
       <c r="G61">
         <v>10.8</v>
@@ -6289,37 +6289,37 @@
         <v>19.2</v>
       </c>
       <c r="M61">
-        <v>22.0081092</v>
+        <v>22.381128</v>
       </c>
       <c r="N61">
-        <v>-2.808109200000001</v>
+        <v>-3.181128000000001</v>
       </c>
       <c r="O61">
-        <v>-0.5335407480000001</v>
+        <v>-0.6044143200000002</v>
       </c>
       <c r="P61">
-        <v>-2.274568452</v>
+        <v>-2.576713680000001</v>
       </c>
       <c r="Q61">
-        <v>3.825431548000001</v>
+        <v>3.52328632</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1533401320560333</v>
+        <v>0.1560286353574342</v>
       </c>
       <c r="T61">
-        <v>1.813281120942257</v>
+        <v>1.858613148965813</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1657570837571089</v>
+        <v>0.1629944656944905</v>
       </c>
       <c r="W61">
-        <v>0.1224668601044564</v>
+        <v>0.1228724124360488</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8724057039847839</v>
+        <v>0.8578656089183708</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.136134901604603</v>
+        <v>0.137144901604603</v>
       </c>
       <c r="C62">
-        <v>-10.2073080894086</v>
+        <v>-14.20177967345384</v>
       </c>
       <c r="D62">
-        <v>131.4526919105914</v>
+        <v>129.9992203265462</v>
       </c>
       <c r="E62">
-        <v>128.46</v>
+        <v>131.001</v>
       </c>
       <c r="F62">
-        <v>152.46</v>
+        <v>155.001</v>
       </c>
       <c r="G62">
         <v>10.8</v>
@@ -6371,37 +6371,37 @@
         <v>19.2</v>
       </c>
       <c r="M62">
-        <v>22.381128</v>
+        <v>22.7541468</v>
       </c>
       <c r="N62">
-        <v>-3.181128000000001</v>
+        <v>-3.554146800000005</v>
       </c>
       <c r="O62">
-        <v>-0.6044143200000002</v>
+        <v>-0.6752878920000009</v>
       </c>
       <c r="P62">
-        <v>-2.576713680000001</v>
+        <v>-2.878858908000004</v>
       </c>
       <c r="Q62">
-        <v>3.52328632</v>
+        <v>3.221141091999997</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1560286353574342</v>
+        <v>0.1588550106230094</v>
       </c>
       <c r="T62">
-        <v>1.858613148965813</v>
+        <v>1.906269896375193</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1629944656944905</v>
+        <v>0.1603224252732693</v>
       </c>
       <c r="W62">
-        <v>0.1228724124360488</v>
+        <v>0.1232646679698841</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8578656089183708</v>
+        <v>0.8438022382803646</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.137144901604603</v>
+        <v>0.1381549016046029</v>
       </c>
       <c r="C63">
-        <v>-14.20177967345384</v>
+        <v>-18.16446071310173</v>
       </c>
       <c r="D63">
-        <v>129.9992203265462</v>
+        <v>128.5775392868983</v>
       </c>
       <c r="E63">
-        <v>131.001</v>
+        <v>133.542</v>
       </c>
       <c r="F63">
-        <v>155.001</v>
+        <v>157.542</v>
       </c>
       <c r="G63">
         <v>10.8</v>
@@ -6453,37 +6453,37 @@
         <v>19.2</v>
       </c>
       <c r="M63">
-        <v>22.7541468</v>
+        <v>23.1271656</v>
       </c>
       <c r="N63">
-        <v>-3.554146800000005</v>
+        <v>-3.927165600000002</v>
       </c>
       <c r="O63">
-        <v>-0.6752878920000009</v>
+        <v>-0.7461614640000004</v>
       </c>
       <c r="P63">
-        <v>-2.878858908000004</v>
+        <v>-3.181004136000002</v>
       </c>
       <c r="Q63">
-        <v>3.221141091999997</v>
+        <v>2.918995864</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1588550106230094</v>
+        <v>0.1618301424815096</v>
       </c>
       <c r="T63">
-        <v>1.906269896375193</v>
+        <v>1.956434893648224</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1603224252732693</v>
+        <v>0.1577365797043456</v>
       </c>
       <c r="W63">
-        <v>0.1232646679698841</v>
+        <v>0.1236442700994021</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8438022382803646</v>
+        <v>0.8301925247597137</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1381549016046029</v>
+        <v>0.139164901604603</v>
       </c>
       <c r="C64">
-        <v>-18.16446071310173</v>
+        <v>-22.09638291671243</v>
       </c>
       <c r="D64">
-        <v>128.5775392868983</v>
+        <v>127.1866170832876</v>
       </c>
       <c r="E64">
-        <v>133.542</v>
+        <v>136.083</v>
       </c>
       <c r="F64">
-        <v>157.542</v>
+        <v>160.083</v>
       </c>
       <c r="G64">
         <v>10.8</v>
@@ -6535,37 +6535,37 @@
         <v>19.2</v>
       </c>
       <c r="M64">
-        <v>23.1271656</v>
+        <v>23.5001844</v>
       </c>
       <c r="N64">
-        <v>-3.927165600000002</v>
+        <v>-4.300184400000003</v>
       </c>
       <c r="O64">
-        <v>-0.7461614640000004</v>
+        <v>-0.8170350360000005</v>
       </c>
       <c r="P64">
-        <v>-3.181004136000002</v>
+        <v>-3.483149364000002</v>
       </c>
       <c r="Q64">
-        <v>2.918995864</v>
+        <v>2.616850635999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1618301424815096</v>
+        <v>0.1649660922783072</v>
       </c>
       <c r="T64">
-        <v>1.956434893648224</v>
+        <v>2.009311512395474</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1577365797043456</v>
+        <v>0.1552328244709433</v>
       </c>
       <c r="W64">
-        <v>0.1236442700994021</v>
+        <v>0.1240118213676655</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8301925247597137</v>
+        <v>0.8170148656365436</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.139164901604603</v>
+        <v>0.1401749016046029</v>
       </c>
       <c r="C65">
-        <v>-22.09638291671243</v>
+        <v>-25.99853382728304</v>
       </c>
       <c r="D65">
-        <v>127.1866170832876</v>
+        <v>125.825466172717</v>
       </c>
       <c r="E65">
-        <v>136.083</v>
+        <v>138.624</v>
       </c>
       <c r="F65">
-        <v>160.083</v>
+        <v>162.624</v>
       </c>
       <c r="G65">
         <v>10.8</v>
@@ -6617,37 +6617,37 @@
         <v>19.2</v>
       </c>
       <c r="M65">
-        <v>23.5001844</v>
+        <v>23.8732032</v>
       </c>
       <c r="N65">
-        <v>-4.300184400000003</v>
+        <v>-4.673203200000003</v>
       </c>
       <c r="O65">
-        <v>-0.8170350360000005</v>
+        <v>-0.8879086080000006</v>
       </c>
       <c r="P65">
-        <v>-3.483149364000002</v>
+        <v>-3.785294592000003</v>
       </c>
       <c r="Q65">
-        <v>2.616850635999999</v>
+        <v>2.314705407999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1649660922783072</v>
+        <v>0.1682762615082602</v>
       </c>
       <c r="T65">
-        <v>2.009311512395474</v>
+        <v>2.065125721073126</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1552328244709433</v>
+        <v>0.1528073115885848</v>
       </c>
       <c r="W65">
-        <v>0.1240118213676655</v>
+        <v>0.1243678866587958</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8170148656365436</v>
+        <v>0.8042490083609726</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1401749016046029</v>
+        <v>0.1775702005800178</v>
       </c>
       <c r="C66">
-        <v>-25.99853382728304</v>
+        <v>-64.24776607963059</v>
       </c>
       <c r="D66">
-        <v>125.825466172717</v>
+        <v>90.1172339203694</v>
       </c>
       <c r="E66">
-        <v>138.624</v>
+        <v>141.165</v>
       </c>
       <c r="F66">
-        <v>162.624</v>
+        <v>165.165</v>
       </c>
       <c r="G66">
         <v>10.8</v>
@@ -6699,45 +6699,45 @@
         <v>19.2</v>
       </c>
       <c r="M66">
-        <v>23.8732032</v>
+        <v>33.165132</v>
       </c>
       <c r="N66">
-        <v>-4.673203200000003</v>
+        <v>-13.965132</v>
       </c>
       <c r="O66">
-        <v>-0.8879086080000006</v>
+        <v>-2.65337508</v>
       </c>
       <c r="P66">
-        <v>-3.785294592000003</v>
+        <v>-11.31175692</v>
       </c>
       <c r="Q66">
-        <v>2.314705407999999</v>
+        <v>-5.211756919999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1682762615082602</v>
+        <v>0.1754478660525385</v>
       </c>
       <c r="T66">
-        <v>2.065125721073126</v>
+        <v>2.186049276571717</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1528073115885848</v>
+        <v>0.1099950393684548</v>
       </c>
       <c r="W66">
-        <v>0.1243678866587958</v>
+        <v>0.1787129960948143</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8042490083609726</v>
+        <v>0.5789212598339726</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1775702005800178</v>
+        <v>0.1791202005800178</v>
       </c>
       <c r="C67">
-        <v>-64.24776607963059</v>
+        <v>-67.83648211942712</v>
       </c>
       <c r="D67">
-        <v>90.1172339203694</v>
+        <v>89.0695178805729</v>
       </c>
       <c r="E67">
-        <v>141.165</v>
+        <v>143.706</v>
       </c>
       <c r="F67">
-        <v>165.165</v>
+        <v>167.706</v>
       </c>
       <c r="G67">
         <v>10.8</v>
@@ -6781,37 +6781,37 @@
         <v>19.2</v>
       </c>
       <c r="M67">
-        <v>33.165132</v>
+        <v>33.6753648</v>
       </c>
       <c r="N67">
-        <v>-13.965132</v>
+        <v>-14.4753648</v>
       </c>
       <c r="O67">
-        <v>-2.65337508</v>
+        <v>-2.750319312000001</v>
       </c>
       <c r="P67">
-        <v>-11.31175692</v>
+        <v>-11.725045488</v>
       </c>
       <c r="Q67">
-        <v>-5.211756919999999</v>
+        <v>-5.625045488000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1754478660525385</v>
+        <v>0.1792610385834955</v>
       </c>
       <c r="T67">
-        <v>2.186049276571717</v>
+        <v>2.250344843529708</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1099950393684548</v>
+        <v>0.1083284478628721</v>
       </c>
       <c r="W67">
-        <v>0.1787129960948143</v>
+        <v>0.1790476476691353</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5789212598339726</v>
+        <v>0.5701497255940638</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1791202005800178</v>
+        <v>0.1806702005800178</v>
       </c>
       <c r="C68">
-        <v>-67.83648211942712</v>
+        <v>-71.40111634048678</v>
       </c>
       <c r="D68">
-        <v>89.0695178805729</v>
+        <v>88.04588365951324</v>
       </c>
       <c r="E68">
-        <v>143.706</v>
+        <v>146.247</v>
       </c>
       <c r="F68">
-        <v>167.706</v>
+        <v>170.247</v>
       </c>
       <c r="G68">
         <v>10.8</v>
@@ -6863,37 +6863,37 @@
         <v>19.2</v>
       </c>
       <c r="M68">
-        <v>33.6753648</v>
+        <v>34.1855976</v>
       </c>
       <c r="N68">
-        <v>-14.4753648</v>
+        <v>-14.9855976</v>
       </c>
       <c r="O68">
-        <v>-2.750319312000001</v>
+        <v>-2.847263544</v>
       </c>
       <c r="P68">
-        <v>-11.725045488</v>
+        <v>-12.138334056</v>
       </c>
       <c r="Q68">
-        <v>-5.625045488000001</v>
+        <v>-6.038334056</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1792610385834955</v>
+        <v>0.1833053124799651</v>
       </c>
       <c r="T68">
-        <v>2.250344843529708</v>
+        <v>2.318537111515457</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1083284478628721</v>
+        <v>0.1067116053574561</v>
       </c>
       <c r="W68">
-        <v>0.1790476476691353</v>
+        <v>0.1793723096442228</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5701497255940638</v>
+        <v>0.5616400281971377</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1806702005800178</v>
+        <v>0.1822202005800178</v>
       </c>
       <c r="C69">
-        <v>-71.40111634048678</v>
+        <v>-74.94248959233667</v>
       </c>
       <c r="D69">
-        <v>88.04588365951324</v>
+        <v>87.04551040766334</v>
       </c>
       <c r="E69">
-        <v>146.247</v>
+        <v>148.788</v>
       </c>
       <c r="F69">
-        <v>170.247</v>
+        <v>172.788</v>
       </c>
       <c r="G69">
         <v>10.8</v>
@@ -6945,37 +6945,37 @@
         <v>19.2</v>
       </c>
       <c r="M69">
-        <v>34.1855976</v>
+        <v>34.69583040000001</v>
       </c>
       <c r="N69">
-        <v>-14.9855976</v>
+        <v>-15.49583040000001</v>
       </c>
       <c r="O69">
-        <v>-2.847263544</v>
+        <v>-2.944207776000001</v>
       </c>
       <c r="P69">
-        <v>-12.138334056</v>
+        <v>-12.55162262400001</v>
       </c>
       <c r="Q69">
-        <v>-6.038334056</v>
+        <v>-6.451622624000004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1833053124799651</v>
+        <v>0.187602353494964</v>
       </c>
       <c r="T69">
-        <v>2.318537111515457</v>
+        <v>2.390991396250315</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1067116053574561</v>
+        <v>0.1051423170433759</v>
       </c>
       <c r="W69">
-        <v>0.1793723096442228</v>
+        <v>0.1796874227376901</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5616400281971377</v>
+        <v>0.5533806160177679</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1822202005800178</v>
+        <v>0.1837702005800178</v>
       </c>
       <c r="C70">
-        <v>-74.94248959233667</v>
+        <v>-78.4613858377917</v>
       </c>
       <c r="D70">
-        <v>87.04551040766334</v>
+        <v>86.06761416220832</v>
       </c>
       <c r="E70">
-        <v>148.788</v>
+        <v>151.329</v>
       </c>
       <c r="F70">
-        <v>172.788</v>
+        <v>175.329</v>
       </c>
       <c r="G70">
         <v>10.8</v>
@@ -7027,37 +7027,37 @@
         <v>19.2</v>
       </c>
       <c r="M70">
-        <v>34.69583040000001</v>
+        <v>35.2060632</v>
       </c>
       <c r="N70">
-        <v>-15.49583040000001</v>
+        <v>-16.0060632</v>
       </c>
       <c r="O70">
-        <v>-2.944207776000001</v>
+        <v>-3.041152008000001</v>
       </c>
       <c r="P70">
-        <v>-12.55162262400001</v>
+        <v>-12.964911192</v>
       </c>
       <c r="Q70">
-        <v>-6.451622624000004</v>
+        <v>-6.864911192000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.187602353494964</v>
+        <v>0.1921766229625435</v>
       </c>
       <c r="T70">
-        <v>2.390991396250315</v>
+        <v>2.468120150968067</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1051423170433759</v>
+        <v>0.1036185153470951</v>
       </c>
       <c r="W70">
-        <v>0.1796874227376901</v>
+        <v>0.1799934021183033</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5533806160177679</v>
+        <v>0.5453606070899741</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1837702005800178</v>
+        <v>0.1853202005800177</v>
       </c>
       <c r="C71">
-        <v>-78.4613858377917</v>
+        <v>-81.9585542019198</v>
       </c>
       <c r="D71">
-        <v>86.06761416220832</v>
+        <v>85.11144579808021</v>
       </c>
       <c r="E71">
-        <v>151.329</v>
+        <v>153.87</v>
       </c>
       <c r="F71">
-        <v>175.329</v>
+        <v>177.87</v>
       </c>
       <c r="G71">
         <v>10.8</v>
@@ -7109,37 +7109,37 @@
         <v>19.2</v>
       </c>
       <c r="M71">
-        <v>35.2060632</v>
+        <v>35.716296</v>
       </c>
       <c r="N71">
-        <v>-16.0060632</v>
+        <v>-16.516296</v>
       </c>
       <c r="O71">
-        <v>-3.041152008000001</v>
+        <v>-3.13809624</v>
       </c>
       <c r="P71">
-        <v>-12.964911192</v>
+        <v>-13.37819976</v>
       </c>
       <c r="Q71">
-        <v>-6.864911192000001</v>
+        <v>-7.27819976</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1921766229625435</v>
+        <v>0.1970558437279616</v>
       </c>
       <c r="T71">
-        <v>2.468120150968067</v>
+        <v>2.550390822667003</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1036185153470951</v>
+        <v>0.1021382508421366</v>
       </c>
       <c r="W71">
-        <v>0.1799934021183033</v>
+        <v>0.180290639230899</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5453606070899741</v>
+        <v>0.5375697412744032</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1853202005800177</v>
+        <v>0.1868702005800178</v>
       </c>
       <c r="C72">
-        <v>-81.9585542019198</v>
+        <v>-85.43471088592973</v>
       </c>
       <c r="D72">
-        <v>85.11144579808021</v>
+        <v>84.17628911407027</v>
       </c>
       <c r="E72">
-        <v>153.87</v>
+        <v>156.411</v>
       </c>
       <c r="F72">
-        <v>177.87</v>
+        <v>180.411</v>
       </c>
       <c r="G72">
         <v>10.8</v>
@@ -7191,37 +7191,37 @@
         <v>19.2</v>
       </c>
       <c r="M72">
-        <v>35.716296</v>
+        <v>36.2265288</v>
       </c>
       <c r="N72">
-        <v>-16.516296</v>
+        <v>-17.0265288</v>
       </c>
       <c r="O72">
-        <v>-3.13809624</v>
+        <v>-3.235040472000001</v>
       </c>
       <c r="P72">
-        <v>-13.37819976</v>
+        <v>-13.791488328</v>
       </c>
       <c r="Q72">
-        <v>-7.27819976</v>
+        <v>-7.691488328000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1970558437279616</v>
+        <v>0.2022715624772017</v>
       </c>
       <c r="T72">
-        <v>2.550390822667003</v>
+        <v>2.638335333793452</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1021382508421366</v>
+        <v>0.1006996839288671</v>
       </c>
       <c r="W72">
-        <v>0.180290639230899</v>
+        <v>0.1805795034670835</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5375697412744032</v>
+        <v>0.5299983364677213</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1868702005800177</v>
+        <v>0.1884202005800177</v>
       </c>
       <c r="C73">
-        <v>-85.4347108859297</v>
+        <v>-88.89054095625771</v>
       </c>
       <c r="D73">
-        <v>84.17628911407027</v>
+        <v>83.26145904374229</v>
       </c>
       <c r="E73">
-        <v>156.411</v>
+        <v>158.952</v>
       </c>
       <c r="F73">
-        <v>180.411</v>
+        <v>182.952</v>
       </c>
       <c r="G73">
         <v>10.8</v>
@@ -7273,37 +7273,37 @@
         <v>19.2</v>
       </c>
       <c r="M73">
-        <v>36.2265288</v>
+        <v>36.7367616</v>
       </c>
       <c r="N73">
-        <v>-17.0265288</v>
+        <v>-17.5367616</v>
       </c>
       <c r="O73">
-        <v>-3.235040472</v>
+        <v>-3.331984704</v>
       </c>
       <c r="P73">
-        <v>-13.791488328</v>
+        <v>-14.204776896</v>
       </c>
       <c r="Q73">
-        <v>-7.691488327999997</v>
+        <v>-8.104776896000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2022715624772016</v>
+        <v>0.2078598325656731</v>
       </c>
       <c r="T73">
-        <v>2.63833533379345</v>
+        <v>2.732561595714645</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1006996839288671</v>
+        <v>0.0993010772076328</v>
       </c>
       <c r="W73">
-        <v>0.1805795034670835</v>
+        <v>0.1808603436967073</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5299983364677214</v>
+        <v>0.5226372484612252</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1884202005800177</v>
+        <v>0.1899702005800178</v>
       </c>
       <c r="C74">
-        <v>-88.89054095625771</v>
+        <v>-92.3267000182455</v>
       </c>
       <c r="D74">
-        <v>83.26145904374229</v>
+        <v>82.36629998175449</v>
       </c>
       <c r="E74">
-        <v>158.952</v>
+        <v>161.493</v>
       </c>
       <c r="F74">
-        <v>182.952</v>
+        <v>185.493</v>
       </c>
       <c r="G74">
         <v>10.8</v>
@@ -7355,37 +7355,37 @@
         <v>19.2</v>
       </c>
       <c r="M74">
-        <v>36.7367616</v>
+        <v>37.2469944</v>
       </c>
       <c r="N74">
-        <v>-17.5367616</v>
+        <v>-18.0469944</v>
       </c>
       <c r="O74">
-        <v>-3.331984704</v>
+        <v>-3.428928936</v>
       </c>
       <c r="P74">
-        <v>-14.204776896</v>
+        <v>-14.618065464</v>
       </c>
       <c r="Q74">
-        <v>-8.104776896000001</v>
+        <v>-8.518065463999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2078598325656731</v>
+        <v>0.2138620485866239</v>
       </c>
       <c r="T74">
-        <v>2.732561595714645</v>
+        <v>2.833767580741113</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.0993010772076328</v>
+        <v>0.09794078847876111</v>
       </c>
       <c r="W74">
-        <v>0.1808603436967073</v>
+        <v>0.1811334896734648</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5226372484612252</v>
+        <v>0.5154778340987427</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1899702005800178</v>
+        <v>0.1915202005800178</v>
       </c>
       <c r="C75">
-        <v>-92.3267000182455</v>
+        <v>-95.7438157830026</v>
       </c>
       <c r="D75">
-        <v>82.36629998175449</v>
+        <v>81.49018421699739</v>
       </c>
       <c r="E75">
-        <v>161.493</v>
+        <v>164.034</v>
       </c>
       <c r="F75">
-        <v>185.493</v>
+        <v>188.034</v>
       </c>
       <c r="G75">
         <v>10.8</v>
@@ -7437,37 +7437,37 @@
         <v>19.2</v>
       </c>
       <c r="M75">
-        <v>37.2469944</v>
+        <v>37.7572272</v>
       </c>
       <c r="N75">
-        <v>-18.0469944</v>
+        <v>-18.5572272</v>
       </c>
       <c r="O75">
-        <v>-3.428928936</v>
+        <v>-3.525873168000001</v>
       </c>
       <c r="P75">
-        <v>-14.618065464</v>
+        <v>-15.031354032</v>
       </c>
       <c r="Q75">
-        <v>-8.518065463999998</v>
+        <v>-8.931354032000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2138620485866239</v>
+        <v>0.2203259735322633</v>
       </c>
       <c r="T75">
-        <v>2.833767580741113</v>
+        <v>2.942758641538849</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09794078847876111</v>
+        <v>0.09661726431012919</v>
       </c>
       <c r="W75">
-        <v>0.1811334896734648</v>
+        <v>0.1813992533265261</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5154778340987427</v>
+        <v>0.5085119174217326</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1915202005800178</v>
+        <v>0.1930702005800178</v>
       </c>
       <c r="C76">
-        <v>-95.7438157830026</v>
+        <v>-99.14248953532234</v>
       </c>
       <c r="D76">
-        <v>81.49018421699739</v>
+        <v>80.63251046467765</v>
       </c>
       <c r="E76">
-        <v>164.034</v>
+        <v>166.575</v>
       </c>
       <c r="F76">
-        <v>188.034</v>
+        <v>190.575</v>
       </c>
       <c r="G76">
         <v>10.8</v>
@@ -7519,37 +7519,37 @@
         <v>19.2</v>
       </c>
       <c r="M76">
-        <v>37.7572272</v>
+        <v>38.26746</v>
       </c>
       <c r="N76">
-        <v>-18.5572272</v>
+        <v>-19.06746</v>
       </c>
       <c r="O76">
-        <v>-3.525873168000001</v>
+        <v>-3.6228174</v>
       </c>
       <c r="P76">
-        <v>-15.031354032</v>
+        <v>-15.4446426</v>
       </c>
       <c r="Q76">
-        <v>-8.931354032000002</v>
+        <v>-9.344642599999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2203259735322633</v>
+        <v>0.2273070124735539</v>
       </c>
       <c r="T76">
-        <v>2.942758641538849</v>
+        <v>3.060468987200403</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09661726431012919</v>
+        <v>0.0953290341193275</v>
       </c>
       <c r="W76">
-        <v>0.1813992533265261</v>
+        <v>0.1816579299488391</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5085119174217326</v>
+        <v>0.5017317585227763</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1930702005800178</v>
+        <v>0.2217388342412876</v>
       </c>
       <c r="C77">
-        <v>-99.14248953532234</v>
+        <v>-114.8222824213211</v>
       </c>
       <c r="D77">
-        <v>80.63251046467765</v>
+        <v>67.49371757867885</v>
       </c>
       <c r="E77">
-        <v>166.575</v>
+        <v>169.116</v>
       </c>
       <c r="F77">
-        <v>190.575</v>
+        <v>193.116</v>
       </c>
       <c r="G77">
         <v>10.8</v>
@@ -7601,45 +7601,45 @@
         <v>19.2</v>
       </c>
       <c r="M77">
-        <v>38.26746</v>
+        <v>45.5367528</v>
       </c>
       <c r="N77">
-        <v>-19.06746</v>
+        <v>-26.3367528</v>
       </c>
       <c r="O77">
-        <v>-3.6228174</v>
+        <v>-5.003983031999999</v>
       </c>
       <c r="P77">
-        <v>-15.4446426</v>
+        <v>-21.332769768</v>
       </c>
       <c r="Q77">
-        <v>-9.344642599999998</v>
+        <v>-15.232769768</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2273070124735539</v>
+        <v>0.2370307782485763</v>
       </c>
       <c r="T77">
-        <v>3.060468987200403</v>
+        <v>3.224425647539313</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0953290341193275</v>
+        <v>0.0801111141152779</v>
       </c>
       <c r="W77">
-        <v>0.1816579299488391</v>
+        <v>0.2169097992916175</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5017317585227763</v>
+        <v>0.4216374427119889</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2217388342412876</v>
+        <v>0.2236388342412876</v>
       </c>
       <c r="C78">
-        <v>-114.8222824213211</v>
+        <v>-118.0843738744146</v>
       </c>
       <c r="D78">
-        <v>67.49371757867885</v>
+        <v>66.77262612558543</v>
       </c>
       <c r="E78">
-        <v>169.116</v>
+        <v>171.657</v>
       </c>
       <c r="F78">
-        <v>193.116</v>
+        <v>195.657</v>
       </c>
       <c r="G78">
         <v>10.8</v>
@@ -7683,37 +7683,37 @@
         <v>19.2</v>
       </c>
       <c r="M78">
-        <v>45.5367528</v>
+        <v>46.13592060000001</v>
       </c>
       <c r="N78">
-        <v>-26.3367528</v>
+        <v>-26.93592060000001</v>
       </c>
       <c r="O78">
-        <v>-5.003983031999999</v>
+        <v>-5.117824914000002</v>
       </c>
       <c r="P78">
-        <v>-21.332769768</v>
+        <v>-21.81809568600001</v>
       </c>
       <c r="Q78">
-        <v>-15.232769768</v>
+        <v>-15.71809568600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2370307782485763</v>
+        <v>0.2453451599115579</v>
       </c>
       <c r="T78">
-        <v>3.224425647539313</v>
+        <v>3.364618066997544</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0801111141152779</v>
+        <v>0.07907071003585868</v>
       </c>
       <c r="W78">
-        <v>0.2169097992916175</v>
+        <v>0.2171551265735445</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4216374427119889</v>
+        <v>0.4161616317676773</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2236388342412876</v>
+        <v>0.2255388342412876</v>
       </c>
       <c r="C79">
-        <v>-118.0843738744146</v>
+        <v>-121.3312201661976</v>
       </c>
       <c r="D79">
-        <v>66.77262612558543</v>
+        <v>66.06677983380243</v>
       </c>
       <c r="E79">
-        <v>171.657</v>
+        <v>174.198</v>
       </c>
       <c r="F79">
-        <v>195.657</v>
+        <v>198.198</v>
       </c>
       <c r="G79">
         <v>10.8</v>
@@ -7765,37 +7765,37 @@
         <v>19.2</v>
       </c>
       <c r="M79">
-        <v>46.13592060000001</v>
+        <v>46.7350884</v>
       </c>
       <c r="N79">
-        <v>-26.93592060000001</v>
+        <v>-27.5350884</v>
       </c>
       <c r="O79">
-        <v>-5.117824914000002</v>
+        <v>-5.231666796000001</v>
       </c>
       <c r="P79">
-        <v>-21.81809568600001</v>
+        <v>-22.303421604</v>
       </c>
       <c r="Q79">
-        <v>-15.71809568600001</v>
+        <v>-16.203421604</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2453451599115579</v>
+        <v>0.2544153944529924</v>
       </c>
       <c r="T79">
-        <v>3.364618066997544</v>
+        <v>3.51755525186107</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07907071003585868</v>
+        <v>0.07805698298411691</v>
       </c>
       <c r="W79">
-        <v>0.2171551265735445</v>
+        <v>0.2173941634123452</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4161616317676773</v>
+        <v>0.4108262262321942</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2255388342412876</v>
+        <v>0.2274388342412876</v>
       </c>
       <c r="C80">
-        <v>-121.3312201661976</v>
+        <v>-124.5632997043842</v>
       </c>
       <c r="D80">
-        <v>66.06677983380243</v>
+        <v>65.37570029561581</v>
       </c>
       <c r="E80">
-        <v>174.198</v>
+        <v>176.739</v>
       </c>
       <c r="F80">
-        <v>198.198</v>
+        <v>200.739</v>
       </c>
       <c r="G80">
         <v>10.8</v>
@@ -7847,37 +7847,37 @@
         <v>19.2</v>
       </c>
       <c r="M80">
-        <v>46.7350884</v>
+        <v>47.33425620000001</v>
       </c>
       <c r="N80">
-        <v>-27.5350884</v>
+        <v>-28.13425620000001</v>
       </c>
       <c r="O80">
-        <v>-5.231666796000001</v>
+        <v>-5.345508678000002</v>
       </c>
       <c r="P80">
-        <v>-22.303421604</v>
+        <v>-22.788747522</v>
       </c>
       <c r="Q80">
-        <v>-16.203421604</v>
+        <v>-16.688747522</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2544153944529924</v>
+        <v>0.2643494608555158</v>
       </c>
       <c r="T80">
-        <v>3.51755525186107</v>
+        <v>3.685057882902073</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07805698298411691</v>
+        <v>0.07706891990836859</v>
       </c>
       <c r="W80">
-        <v>0.2173941634123452</v>
+        <v>0.2176271486856067</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4108262262321942</v>
+        <v>0.4056258942545715</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2274388342412876</v>
+        <v>0.2293388342412876</v>
       </c>
       <c r="C81">
-        <v>-124.5632997043842</v>
+        <v>-127.7810710867194</v>
       </c>
       <c r="D81">
-        <v>65.37570029561581</v>
+        <v>64.6989289132806</v>
       </c>
       <c r="E81">
-        <v>176.739</v>
+        <v>179.28</v>
       </c>
       <c r="F81">
-        <v>200.739</v>
+        <v>203.28</v>
       </c>
       <c r="G81">
         <v>10.8</v>
@@ -7929,37 +7929,37 @@
         <v>19.2</v>
       </c>
       <c r="M81">
-        <v>47.33425620000001</v>
+        <v>47.933424</v>
       </c>
       <c r="N81">
-        <v>-28.13425620000001</v>
+        <v>-28.733424</v>
       </c>
       <c r="O81">
-        <v>-5.345508678000002</v>
+        <v>-5.459350560000001</v>
       </c>
       <c r="P81">
-        <v>-22.788747522</v>
+        <v>-23.27407344</v>
       </c>
       <c r="Q81">
-        <v>-16.688747522</v>
+        <v>-17.17407344</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2643494608555158</v>
+        <v>0.2752769338982916</v>
       </c>
       <c r="T81">
-        <v>3.685057882902073</v>
+        <v>3.869310777047176</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07706891990836859</v>
+        <v>0.07610555840951398</v>
       </c>
       <c r="W81">
-        <v>0.2176271486856067</v>
+        <v>0.2178543093270366</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4056258942545715</v>
+        <v>0.4005555705763895</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2293388342412876</v>
+        <v>0.2312388342412876</v>
       </c>
       <c r="C82">
-        <v>-127.7810710867194</v>
+        <v>-130.9849741158405</v>
       </c>
       <c r="D82">
-        <v>64.6989289132806</v>
+        <v>64.03602588415951</v>
       </c>
       <c r="E82">
-        <v>179.28</v>
+        <v>181.821</v>
       </c>
       <c r="F82">
-        <v>203.28</v>
+        <v>205.821</v>
       </c>
       <c r="G82">
         <v>10.8</v>
@@ -8011,37 +8011,37 @@
         <v>19.2</v>
       </c>
       <c r="M82">
-        <v>47.933424</v>
+        <v>48.5325918</v>
       </c>
       <c r="N82">
-        <v>-28.733424</v>
+        <v>-29.3325918</v>
       </c>
       <c r="O82">
-        <v>-5.459350560000001</v>
+        <v>-5.573192442</v>
       </c>
       <c r="P82">
-        <v>-23.27407344</v>
+        <v>-23.759399358</v>
       </c>
       <c r="Q82">
-        <v>-17.17407344</v>
+        <v>-17.659399358</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2752769338982916</v>
+        <v>0.2873546672613596</v>
       </c>
       <c r="T82">
-        <v>3.869310777047176</v>
+        <v>4.072958712681238</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07610555840951398</v>
+        <v>0.07516598361433481</v>
       </c>
       <c r="W82">
-        <v>0.2178543093270366</v>
+        <v>0.2180758610637399</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4005555705763895</v>
+        <v>0.3956104400754463</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2312388342412876</v>
+        <v>0.2331388342412876</v>
       </c>
       <c r="C83">
-        <v>-130.9849741158405</v>
+        <v>-134.1754307523817</v>
       </c>
       <c r="D83">
-        <v>64.03602588415951</v>
+        <v>63.38656924761828</v>
       </c>
       <c r="E83">
-        <v>181.821</v>
+        <v>184.362</v>
       </c>
       <c r="F83">
-        <v>205.821</v>
+        <v>208.362</v>
       </c>
       <c r="G83">
         <v>10.8</v>
@@ -8093,37 +8093,37 @@
         <v>19.2</v>
       </c>
       <c r="M83">
-        <v>48.5325918</v>
+        <v>49.13175960000001</v>
       </c>
       <c r="N83">
-        <v>-29.3325918</v>
+        <v>-29.93175960000001</v>
       </c>
       <c r="O83">
-        <v>-5.573192442</v>
+        <v>-5.687034324000002</v>
       </c>
       <c r="P83">
-        <v>-23.759399358</v>
+        <v>-24.24472527600001</v>
       </c>
       <c r="Q83">
-        <v>-17.659399358</v>
+        <v>-18.14472527600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2873546672613596</v>
+        <v>0.3007743709981018</v>
       </c>
       <c r="T83">
-        <v>4.072958712681238</v>
+        <v>4.299234196719086</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07516598361433481</v>
+        <v>0.07424932527757462</v>
       </c>
       <c r="W83">
-        <v>0.2180758610637399</v>
+        <v>0.2182920090995479</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3956104400754463</v>
+        <v>0.3907859225135506</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2331388342412876</v>
+        <v>0.2350388342412876</v>
       </c>
       <c r="C84">
-        <v>-134.1754307523817</v>
+        <v>-137.3528460106628</v>
       </c>
       <c r="D84">
-        <v>63.38656924761828</v>
+        <v>62.75015398933722</v>
       </c>
       <c r="E84">
-        <v>184.362</v>
+        <v>186.903</v>
       </c>
       <c r="F84">
-        <v>208.362</v>
+        <v>210.903</v>
       </c>
       <c r="G84">
         <v>10.8</v>
@@ -8175,37 +8175,37 @@
         <v>19.2</v>
       </c>
       <c r="M84">
-        <v>49.13175960000001</v>
+        <v>49.73092740000001</v>
       </c>
       <c r="N84">
-        <v>-29.93175960000001</v>
+        <v>-30.53092740000001</v>
       </c>
       <c r="O84">
-        <v>-5.687034324000002</v>
+        <v>-5.800876206000002</v>
       </c>
       <c r="P84">
-        <v>-24.24472527600001</v>
+        <v>-24.730051194</v>
       </c>
       <c r="Q84">
-        <v>-18.14472527600001</v>
+        <v>-18.630051194</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3007743709981018</v>
+        <v>0.3157728634097549</v>
       </c>
       <c r="T84">
-        <v>4.299234196719086</v>
+        <v>4.552130325937856</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07424932527757462</v>
+        <v>0.07335475509350746</v>
       </c>
       <c r="W84">
-        <v>0.2182920090995479</v>
+        <v>0.218502948748951</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3907859225135506</v>
+        <v>0.3860776583868814</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2350388342412876</v>
+        <v>0.2369388342412876</v>
       </c>
       <c r="C85">
-        <v>-137.3528460106628</v>
+        <v>-140.517608800956</v>
       </c>
       <c r="D85">
-        <v>62.75015398933722</v>
+        <v>62.126391199044</v>
       </c>
       <c r="E85">
-        <v>186.903</v>
+        <v>189.444</v>
       </c>
       <c r="F85">
-        <v>210.903</v>
+        <v>213.444</v>
       </c>
       <c r="G85">
         <v>10.8</v>
@@ -8257,37 +8257,37 @@
         <v>19.2</v>
       </c>
       <c r="M85">
-        <v>49.73092740000001</v>
+        <v>50.33009520000001</v>
       </c>
       <c r="N85">
-        <v>-30.53092740000001</v>
+        <v>-31.13009520000001</v>
       </c>
       <c r="O85">
-        <v>-5.800876206000002</v>
+        <v>-5.914718088000002</v>
       </c>
       <c r="P85">
-        <v>-24.730051194</v>
+        <v>-25.21537711200001</v>
       </c>
       <c r="Q85">
-        <v>-18.630051194</v>
+        <v>-19.11537711200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3157728634097549</v>
+        <v>0.3326461673728646</v>
       </c>
       <c r="T85">
-        <v>4.552130325937856</v>
+        <v>4.836638471308972</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07335475509350746</v>
+        <v>0.07248148419953712</v>
       </c>
       <c r="W85">
-        <v>0.218502948748951</v>
+        <v>0.2187088660257492</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3860776583868814</v>
+        <v>0.3814814957870375</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2369388342412876</v>
+        <v>0.2388388342412876</v>
       </c>
       <c r="C86">
-        <v>-140.517608800956</v>
+        <v>-143.6700927220132</v>
       </c>
       <c r="D86">
-        <v>62.126391199044</v>
+        <v>61.51490727798673</v>
       </c>
       <c r="E86">
-        <v>189.444</v>
+        <v>191.985</v>
       </c>
       <c r="F86">
-        <v>213.444</v>
+        <v>215.985</v>
       </c>
       <c r="G86">
         <v>10.8</v>
@@ -8339,37 +8339,37 @@
         <v>19.2</v>
       </c>
       <c r="M86">
-        <v>50.3300952</v>
+        <v>50.929263</v>
       </c>
       <c r="N86">
-        <v>-31.1300952</v>
+        <v>-31.729263</v>
       </c>
       <c r="O86">
-        <v>-5.914718088000001</v>
+        <v>-6.02855997</v>
       </c>
       <c r="P86">
-        <v>-25.215377112</v>
+        <v>-25.70070303</v>
       </c>
       <c r="Q86">
-        <v>-19.115377112</v>
+        <v>-19.60070303</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3326461673728645</v>
+        <v>0.3517692451977221</v>
       </c>
       <c r="T86">
-        <v>4.836638471308969</v>
+        <v>5.159081036062901</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07248148419953714</v>
+        <v>0.07162876085601316</v>
       </c>
       <c r="W86">
-        <v>0.2187088660257492</v>
+        <v>0.2189099381901521</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3814814957870375</v>
+        <v>0.376993478189543</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2388388342412876</v>
+        <v>0.2407388342412876</v>
       </c>
       <c r="C87">
-        <v>-143.6700927220132</v>
+        <v>-146.8106568072458</v>
       </c>
       <c r="D87">
-        <v>61.51490727798673</v>
+        <v>60.9153431927542</v>
       </c>
       <c r="E87">
-        <v>191.985</v>
+        <v>194.526</v>
       </c>
       <c r="F87">
-        <v>215.985</v>
+        <v>218.526</v>
       </c>
       <c r="G87">
         <v>10.8</v>
@@ -8421,37 +8421,37 @@
         <v>19.2</v>
       </c>
       <c r="M87">
-        <v>50.929263</v>
+        <v>51.5284308</v>
       </c>
       <c r="N87">
-        <v>-31.729263</v>
+        <v>-32.32843079999999</v>
       </c>
       <c r="O87">
-        <v>-6.02855997</v>
+        <v>-6.142401851999999</v>
       </c>
       <c r="P87">
-        <v>-25.70070303</v>
+        <v>-26.18602894799999</v>
       </c>
       <c r="Q87">
-        <v>-19.60070303</v>
+        <v>-20.08602894799999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3517692451977221</v>
+        <v>0.3736241912832736</v>
       </c>
       <c r="T87">
-        <v>5.159081036062901</v>
+        <v>5.527586824353108</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07162876085601316</v>
+        <v>0.07079586828792001</v>
       </c>
       <c r="W87">
-        <v>0.2189099381901521</v>
+        <v>0.2191063342577085</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.376993478189543</v>
+        <v>0.3726098330943158</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2407388342412876</v>
+        <v>0.2426388342412876</v>
       </c>
       <c r="C88">
-        <v>-146.8106568072458</v>
+        <v>-149.9396462276889</v>
       </c>
       <c r="D88">
-        <v>60.9153431927542</v>
+        <v>60.3273537723111</v>
       </c>
       <c r="E88">
-        <v>194.526</v>
+        <v>197.067</v>
       </c>
       <c r="F88">
-        <v>218.526</v>
+        <v>221.067</v>
       </c>
       <c r="G88">
         <v>10.8</v>
@@ -8503,37 +8503,37 @@
         <v>19.2</v>
       </c>
       <c r="M88">
-        <v>51.5284308</v>
+        <v>52.12759860000001</v>
       </c>
       <c r="N88">
-        <v>-32.32843079999999</v>
+        <v>-32.92759860000001</v>
       </c>
       <c r="O88">
-        <v>-6.142401851999999</v>
+        <v>-6.256243734000002</v>
       </c>
       <c r="P88">
-        <v>-26.18602894799999</v>
+        <v>-26.67135486600001</v>
       </c>
       <c r="Q88">
-        <v>-20.08602894799999</v>
+        <v>-20.57135486600001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3736241912832736</v>
+        <v>0.3988414367666024</v>
       </c>
       <c r="T88">
-        <v>5.527586824353108</v>
+        <v>5.952785810841808</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07079586828792001</v>
+        <v>0.06998212267541516</v>
       </c>
       <c r="W88">
-        <v>0.2191063342577085</v>
+        <v>0.2192982154731371</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3726098330943158</v>
+        <v>0.3683269614495533</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2426388342412876</v>
+        <v>0.2445388342412876</v>
       </c>
       <c r="C89">
-        <v>-149.9396462276889</v>
+        <v>-153.0573929546433</v>
       </c>
       <c r="D89">
-        <v>60.3273537723111</v>
+        <v>59.7506070453567</v>
       </c>
       <c r="E89">
-        <v>197.067</v>
+        <v>199.608</v>
       </c>
       <c r="F89">
-        <v>221.067</v>
+        <v>223.608</v>
       </c>
       <c r="G89">
         <v>10.8</v>
@@ -8585,37 +8585,37 @@
         <v>19.2</v>
       </c>
       <c r="M89">
-        <v>52.12759860000001</v>
+        <v>52.7267664</v>
       </c>
       <c r="N89">
-        <v>-32.92759860000001</v>
+        <v>-33.5267664</v>
       </c>
       <c r="O89">
-        <v>-6.256243734000002</v>
+        <v>-6.370085616</v>
       </c>
       <c r="P89">
-        <v>-26.67135486600001</v>
+        <v>-27.156680784</v>
       </c>
       <c r="Q89">
-        <v>-20.57135486600001</v>
+        <v>-21.056680784</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3988414367666024</v>
+        <v>0.4282615564971526</v>
       </c>
       <c r="T89">
-        <v>5.952785810841808</v>
+        <v>6.448851295078627</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06998212267541516</v>
+        <v>0.06918687128137635</v>
       </c>
       <c r="W89">
-        <v>0.2192982154731371</v>
+        <v>0.2194857357518515</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3683269614495533</v>
+        <v>0.3641414277967178</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2445388342412876</v>
+        <v>0.2464388342412876</v>
       </c>
       <c r="C90">
-        <v>-153.0573929546433</v>
+        <v>-156.1642163846661</v>
       </c>
       <c r="D90">
-        <v>59.7506070453567</v>
+        <v>59.18478361533393</v>
       </c>
       <c r="E90">
-        <v>199.608</v>
+        <v>202.149</v>
       </c>
       <c r="F90">
-        <v>223.608</v>
+        <v>226.149</v>
       </c>
       <c r="G90">
         <v>10.8</v>
@@ -8667,37 +8667,37 @@
         <v>19.2</v>
       </c>
       <c r="M90">
-        <v>52.7267664</v>
+        <v>53.3259342</v>
       </c>
       <c r="N90">
-        <v>-33.5267664</v>
+        <v>-34.1259342</v>
       </c>
       <c r="O90">
-        <v>-6.370085616</v>
+        <v>-6.483927498000001</v>
       </c>
       <c r="P90">
-        <v>-27.156680784</v>
+        <v>-27.642006702</v>
       </c>
       <c r="Q90">
-        <v>-21.056680784</v>
+        <v>-21.542006702</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4282615564971526</v>
+        <v>0.4630307889059848</v>
       </c>
       <c r="T90">
-        <v>6.448851295078627</v>
+        <v>7.035110503722139</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06918687128137635</v>
+        <v>0.06840949070518113</v>
       </c>
       <c r="W90">
-        <v>0.2194857357518515</v>
+        <v>0.2196690420917183</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3641414277967178</v>
+        <v>0.3600499510799006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2464388342412876</v>
+        <v>0.2483388342412876</v>
       </c>
       <c r="C91">
-        <v>-156.1642163846661</v>
+        <v>-159.260423929384</v>
       </c>
       <c r="D91">
-        <v>59.18478361533393</v>
+        <v>58.629576070616</v>
       </c>
       <c r="E91">
-        <v>202.149</v>
+        <v>204.69</v>
       </c>
       <c r="F91">
-        <v>226.149</v>
+        <v>228.69</v>
       </c>
       <c r="G91">
         <v>10.8</v>
@@ -8749,37 +8749,37 @@
         <v>19.2</v>
       </c>
       <c r="M91">
-        <v>53.3259342</v>
+        <v>53.925102</v>
       </c>
       <c r="N91">
-        <v>-34.1259342</v>
+        <v>-34.72510200000001</v>
       </c>
       <c r="O91">
-        <v>-6.483927498000001</v>
+        <v>-6.597769380000002</v>
       </c>
       <c r="P91">
-        <v>-27.642006702</v>
+        <v>-28.12733262</v>
       </c>
       <c r="Q91">
-        <v>-21.542006702</v>
+        <v>-22.02733262</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4630307889059848</v>
+        <v>0.5047538677965832</v>
       </c>
       <c r="T91">
-        <v>7.035110503722139</v>
+        <v>7.738621554094353</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06840949070518113</v>
+        <v>0.06764938525290132</v>
       </c>
       <c r="W91">
-        <v>0.2196690420917183</v>
+        <v>0.2198482749573659</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3600499510799006</v>
+        <v>0.3560493960679016</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2483388342412876</v>
+        <v>0.2502388342412876</v>
       </c>
       <c r="C92">
-        <v>-159.260423929384</v>
+        <v>-162.3463115724171</v>
       </c>
       <c r="D92">
-        <v>58.629576070616</v>
+        <v>58.08468842758292</v>
       </c>
       <c r="E92">
-        <v>204.69</v>
+        <v>207.231</v>
       </c>
       <c r="F92">
-        <v>228.69</v>
+        <v>231.231</v>
       </c>
       <c r="G92">
         <v>10.8</v>
@@ -8831,37 +8831,37 @@
         <v>19.2</v>
       </c>
       <c r="M92">
-        <v>53.925102</v>
+        <v>54.5242698</v>
       </c>
       <c r="N92">
-        <v>-34.72510200000001</v>
+        <v>-35.3242698</v>
       </c>
       <c r="O92">
-        <v>-6.597769380000002</v>
+        <v>-6.711611261999999</v>
       </c>
       <c r="P92">
-        <v>-28.12733262</v>
+        <v>-28.612658538</v>
       </c>
       <c r="Q92">
-        <v>-22.02733262</v>
+        <v>-22.512658538</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5047538677965832</v>
+        <v>0.5557487419962036</v>
       </c>
       <c r="T92">
-        <v>7.738621554094353</v>
+        <v>8.598468393438171</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06764938525290132</v>
+        <v>0.06690598541495736</v>
       </c>
       <c r="W92">
-        <v>0.2198482749573659</v>
+        <v>0.2200235686391531</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3560493960679016</v>
+        <v>0.3521367653418809</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2502388342412876</v>
+        <v>0.2521388342412876</v>
       </c>
       <c r="C93">
-        <v>-162.3463115724171</v>
+        <v>-165.422164395533</v>
       </c>
       <c r="D93">
-        <v>58.08468842758292</v>
+        <v>57.54983560446697</v>
       </c>
       <c r="E93">
-        <v>207.231</v>
+        <v>209.772</v>
       </c>
       <c r="F93">
-        <v>231.231</v>
+        <v>233.772</v>
       </c>
       <c r="G93">
         <v>10.8</v>
@@ -8913,37 +8913,37 @@
         <v>19.2</v>
       </c>
       <c r="M93">
-        <v>54.5242698</v>
+        <v>55.1234376</v>
       </c>
       <c r="N93">
-        <v>-35.3242698</v>
+        <v>-35.9234376</v>
       </c>
       <c r="O93">
-        <v>-6.711611261999999</v>
+        <v>-6.825453144</v>
       </c>
       <c r="P93">
-        <v>-28.612658538</v>
+        <v>-29.097984456</v>
       </c>
       <c r="Q93">
-        <v>-22.512658538</v>
+        <v>-22.997984456</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5557487419962036</v>
+        <v>0.6194923347457291</v>
       </c>
       <c r="T93">
-        <v>8.598468393438171</v>
+        <v>9.673276942617944</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06690598541495736</v>
+        <v>0.06617874644305564</v>
       </c>
       <c r="W93">
-        <v>0.2200235686391531</v>
+        <v>0.2201950515887275</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3521367653418809</v>
+        <v>0.3483091918055561</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2521388342412876</v>
+        <v>0.2540388342412876</v>
       </c>
       <c r="C94">
-        <v>-165.422164395533</v>
+        <v>-168.4882570759972</v>
       </c>
       <c r="D94">
-        <v>57.54983560446697</v>
+        <v>57.0247429240028</v>
       </c>
       <c r="E94">
-        <v>209.772</v>
+        <v>212.313</v>
       </c>
       <c r="F94">
-        <v>233.772</v>
+        <v>236.313</v>
       </c>
       <c r="G94">
         <v>10.8</v>
@@ -8995,37 +8995,37 @@
         <v>19.2</v>
       </c>
       <c r="M94">
-        <v>55.1234376</v>
+        <v>55.72260540000001</v>
       </c>
       <c r="N94">
-        <v>-35.9234376</v>
+        <v>-36.5226054</v>
       </c>
       <c r="O94">
-        <v>-6.825453144</v>
+        <v>-6.939295026000001</v>
       </c>
       <c r="P94">
-        <v>-29.097984456</v>
+        <v>-29.583310374</v>
       </c>
       <c r="Q94">
-        <v>-22.997984456</v>
+        <v>-23.483310374</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6194923347457291</v>
+        <v>0.7014483825665477</v>
       </c>
       <c r="T94">
-        <v>9.673276942617944</v>
+        <v>11.05517364870622</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06617874644305564</v>
+        <v>0.06546714701893676</v>
       </c>
       <c r="W94">
-        <v>0.2201950515887275</v>
+        <v>0.2203628467329347</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3483091918055561</v>
+        <v>0.3445639316786145</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2540388342412876</v>
+        <v>0.2559388342412876</v>
       </c>
       <c r="C95">
-        <v>-168.4882570759972</v>
+        <v>-171.5448543569415</v>
       </c>
       <c r="D95">
-        <v>57.0247429240028</v>
+        <v>56.50914564305854</v>
       </c>
       <c r="E95">
-        <v>212.313</v>
+        <v>214.854</v>
       </c>
       <c r="F95">
-        <v>236.313</v>
+        <v>238.854</v>
       </c>
       <c r="G95">
         <v>10.8</v>
@@ -9077,37 +9077,37 @@
         <v>19.2</v>
       </c>
       <c r="M95">
-        <v>55.72260540000001</v>
+        <v>56.3217732</v>
       </c>
       <c r="N95">
-        <v>-36.5226054</v>
+        <v>-37.12177320000001</v>
       </c>
       <c r="O95">
-        <v>-6.939295026000001</v>
+        <v>-7.053136908000002</v>
       </c>
       <c r="P95">
-        <v>-29.583310374</v>
+        <v>-30.068636292</v>
       </c>
       <c r="Q95">
-        <v>-23.483310374</v>
+        <v>-23.968636292</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7014483825665477</v>
+        <v>0.8107231129943059</v>
       </c>
       <c r="T95">
-        <v>11.05517364870622</v>
+        <v>12.89770259015726</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06546714701893676</v>
+        <v>0.06477068800809702</v>
       </c>
       <c r="W95">
-        <v>0.2203628467329347</v>
+        <v>0.2205270717676907</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3445639316786145</v>
+        <v>0.3408983579373527</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2559388342412876</v>
+        <v>0.2578388342412876</v>
       </c>
       <c r="C96">
-        <v>-171.5448543569415</v>
+        <v>-174.5922114924445</v>
       </c>
       <c r="D96">
-        <v>56.50914564305854</v>
+        <v>56.00278850755554</v>
       </c>
       <c r="E96">
-        <v>214.854</v>
+        <v>217.395</v>
       </c>
       <c r="F96">
-        <v>238.854</v>
+        <v>241.395</v>
       </c>
       <c r="G96">
         <v>10.8</v>
@@ -9159,37 +9159,37 @@
         <v>19.2</v>
       </c>
       <c r="M96">
-        <v>56.3217732</v>
+        <v>56.92094100000001</v>
       </c>
       <c r="N96">
-        <v>-37.12177320000001</v>
+        <v>-37.72094100000001</v>
       </c>
       <c r="O96">
-        <v>-7.053136908000002</v>
+        <v>-7.166978790000002</v>
       </c>
       <c r="P96">
-        <v>-30.068636292</v>
+        <v>-30.55396221000001</v>
       </c>
       <c r="Q96">
-        <v>-23.968636292</v>
+        <v>-24.45396221000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8107231129943059</v>
+        <v>0.9637077355931676</v>
       </c>
       <c r="T96">
-        <v>12.89770259015726</v>
+        <v>15.47724310818873</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06477068800809702</v>
+        <v>0.06408889129222231</v>
       </c>
       <c r="W96">
-        <v>0.2205270717676907</v>
+        <v>0.220687839433294</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3408983579373527</v>
+        <v>0.337309954169591</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2578388342412876</v>
+        <v>0.2597388342412876</v>
       </c>
       <c r="C97">
-        <v>-174.5922114924445</v>
+        <v>-177.6305746688949</v>
       </c>
       <c r="D97">
-        <v>56.00278850755554</v>
+        <v>55.50542533110509</v>
       </c>
       <c r="E97">
-        <v>217.395</v>
+        <v>219.936</v>
       </c>
       <c r="F97">
-        <v>241.395</v>
+        <v>243.936</v>
       </c>
       <c r="G97">
         <v>10.8</v>
@@ -9241,37 +9241,37 @@
         <v>19.2</v>
       </c>
       <c r="M97">
-        <v>56.92094100000001</v>
+        <v>57.5201088</v>
       </c>
       <c r="N97">
-        <v>-37.72094100000001</v>
+        <v>-38.3201088</v>
       </c>
       <c r="O97">
-        <v>-7.166978790000002</v>
+        <v>-7.280820672</v>
       </c>
       <c r="P97">
-        <v>-30.55396221000001</v>
+        <v>-31.039288128</v>
       </c>
       <c r="Q97">
-        <v>-24.45396221000001</v>
+        <v>-24.939288128</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9637077355931676</v>
+        <v>1.19318466949146</v>
       </c>
       <c r="T97">
-        <v>15.47724310818873</v>
+        <v>19.34655388523592</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06408889129222231</v>
+        <v>0.06342129867459499</v>
       </c>
       <c r="W97">
-        <v>0.220687839433294</v>
+        <v>0.2208452577725305</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.337309954169591</v>
+        <v>0.333796308813658</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2597388342412876</v>
+        <v>0.2616388342412876</v>
       </c>
       <c r="C98">
-        <v>-177.6305746688949</v>
+        <v>-180.6601814040999</v>
       </c>
       <c r="D98">
-        <v>55.50542533110509</v>
+        <v>55.01681859590003</v>
       </c>
       <c r="E98">
-        <v>219.936</v>
+        <v>222.477</v>
       </c>
       <c r="F98">
-        <v>243.936</v>
+        <v>246.477</v>
       </c>
       <c r="G98">
         <v>10.8</v>
@@ -9323,37 +9323,37 @@
         <v>19.2</v>
       </c>
       <c r="M98">
-        <v>57.5201088</v>
+        <v>58.1192766</v>
       </c>
       <c r="N98">
-        <v>-38.3201088</v>
+        <v>-38.9192766</v>
       </c>
       <c r="O98">
-        <v>-7.280820672</v>
+        <v>-7.394662554000001</v>
       </c>
       <c r="P98">
-        <v>-31.039288128</v>
+        <v>-31.524614046</v>
       </c>
       <c r="Q98">
-        <v>-24.939288128</v>
+        <v>-25.424614046</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.193184669491457</v>
+        <v>1.575646225988609</v>
       </c>
       <c r="T98">
-        <v>19.34655388523586</v>
+        <v>25.79540518031449</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06342129867459501</v>
+        <v>0.06276747085320741</v>
       </c>
       <c r="W98">
-        <v>0.2208452577725305</v>
+        <v>0.2209994303728137</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3337963088136578</v>
+        <v>0.3303551097537232</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2616388342412876</v>
+        <v>0.2635388342412876</v>
       </c>
       <c r="C99">
-        <v>-180.6601814040999</v>
+        <v>-183.6812609254975</v>
       </c>
       <c r="D99">
-        <v>55.01681859590003</v>
+        <v>54.53673907450252</v>
       </c>
       <c r="E99">
-        <v>222.477</v>
+        <v>225.018</v>
       </c>
       <c r="F99">
-        <v>246.477</v>
+        <v>249.018</v>
       </c>
       <c r="G99">
         <v>10.8</v>
@@ -9405,37 +9405,37 @@
         <v>19.2</v>
       </c>
       <c r="M99">
-        <v>58.1192766</v>
+        <v>58.7184444</v>
       </c>
       <c r="N99">
-        <v>-38.9192766</v>
+        <v>-39.51844440000001</v>
       </c>
       <c r="O99">
-        <v>-7.394662554000001</v>
+        <v>-7.508504436000002</v>
       </c>
       <c r="P99">
-        <v>-31.524614046</v>
+        <v>-32.009939964</v>
       </c>
       <c r="Q99">
-        <v>-25.424614046</v>
+        <v>-25.909939964</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.575646225988609</v>
+        <v>2.340569338982914</v>
       </c>
       <c r="T99">
-        <v>25.79540518031449</v>
+        <v>38.69310777047173</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06276747085320741</v>
+        <v>0.06212698645674612</v>
       </c>
       <c r="W99">
-        <v>0.2209994303728137</v>
+        <v>0.2211504565934993</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3303551097537232</v>
+        <v>0.3269841392460321</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2635388342412876</v>
+        <v>0.2654388342412876</v>
       </c>
       <c r="C100">
-        <v>-183.6812609254975</v>
+        <v>-186.694034528738</v>
       </c>
       <c r="D100">
-        <v>54.53673907450252</v>
+        <v>54.06496547126202</v>
       </c>
       <c r="E100">
-        <v>225.018</v>
+        <v>227.559</v>
       </c>
       <c r="F100">
-        <v>249.018</v>
+        <v>251.559</v>
       </c>
       <c r="G100">
         <v>10.8</v>
@@ -9487,37 +9487,37 @@
         <v>19.2</v>
       </c>
       <c r="M100">
-        <v>58.7184444</v>
+        <v>59.3176122</v>
       </c>
       <c r="N100">
-        <v>-39.51844440000001</v>
+        <v>-40.1176122</v>
       </c>
       <c r="O100">
-        <v>-7.508504436000002</v>
+        <v>-7.622346317999999</v>
       </c>
       <c r="P100">
-        <v>-32.009939964</v>
+        <v>-32.495265882</v>
       </c>
       <c r="Q100">
-        <v>-25.909939964</v>
+        <v>-26.395265882</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.340569338982914</v>
+        <v>4.635338677965827</v>
       </c>
       <c r="T100">
-        <v>38.69310777047173</v>
+        <v>77.38621554094345</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06212698645674612</v>
+        <v>0.06149944113900121</v>
       </c>
       <c r="W100">
-        <v>0.2211504565934993</v>
+        <v>0.2212984317794235</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3269841392460321</v>
+        <v>0.323681269152638</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2654388342412876</v>
-      </c>
-      <c r="C101">
-        <v>-186.694034528738</v>
-      </c>
-      <c r="D101">
-        <v>54.06496547126202</v>
-      </c>
-      <c r="E101">
-        <v>227.559</v>
-      </c>
-      <c r="F101">
-        <v>251.559</v>
-      </c>
-      <c r="G101">
-        <v>10.8</v>
-      </c>
-      <c r="H101">
-        <v>230.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>25.3</v>
-      </c>
-      <c r="K101">
-        <v>6.100000000000001</v>
-      </c>
-      <c r="L101">
-        <v>19.2</v>
-      </c>
-      <c r="M101">
-        <v>59.3176122</v>
-      </c>
-      <c r="N101">
-        <v>-40.1176122</v>
-      </c>
-      <c r="O101">
-        <v>-7.622346317999999</v>
-      </c>
-      <c r="P101">
-        <v>-32.495265882</v>
-      </c>
-      <c r="Q101">
-        <v>-26.395265882</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.635338677965827</v>
-      </c>
-      <c r="T101">
-        <v>77.38621554094345</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06149944113900121</v>
-      </c>
-      <c r="W101">
-        <v>0.2212984317794235</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.323681269152638</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
